--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/23,07,26 ПОКОМ КИ/дв 23,07,26 бррсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/23,07,26 ПОКОМ КИ/дв 23,07,26 бррсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\23,07,26 ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\23,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008166A6-C3CD-4F1E-A793-EC58D3A28930}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB718525-D91A-4BC4-9CEA-CEDBC9C5A9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$131</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -678,7 +670,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -692,7 +684,6 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -1016,7 +1007,8 @@
     <col min="24" max="33" width="6" customWidth="1"/>
     <col min="34" max="34" width="33.7109375" customWidth="1"/>
     <col min="35" max="35" width="7" customWidth="1"/>
-    <col min="36" max="46" width="3" customWidth="1"/>
+    <col min="36" max="36" width="10.28515625" customWidth="1"/>
+    <col min="37" max="46" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
@@ -1040,7 +1032,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="15">
+      <c r="U1" s="14">
         <v>2.02</v>
       </c>
       <c r="V1" s="1"/>
@@ -1540,7 +1532,10 @@
         <f>ROUND(G6*U6,0)</f>
         <v>281</v>
       </c>
-      <c r="AJ6" s="1"/>
+      <c r="AJ6" s="1">
+        <f t="shared" ref="AJ6:AJ26" si="3">(S6+X6+Y6+Z6+AA6+AB6+AC6+AD6+AE6+AF6+AG6)/11*7</f>
+        <v>369.43314545454547</v>
+      </c>
       <c r="AK6" s="1"/>
       <c r="AL6" s="1"/>
       <c r="AM6" s="1"/>
@@ -1599,20 +1594,20 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S70" si="3">E7/5</f>
+        <f t="shared" ref="S7:S70" si="4">E7/5</f>
         <v>17.161999999999999</v>
       </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5">
-        <f t="shared" ref="U7:U70" si="4">T7</f>
+        <f t="shared" ref="U7:U70" si="5">T7</f>
         <v>0</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" ref="V7:V70" si="5">(F7+O7+P7+Q7+R7+U7)/S7</f>
+        <f t="shared" ref="V7:V70" si="6">(F7+O7+P7+Q7+R7+U7)/S7</f>
         <v>60.770408460552396</v>
       </c>
       <c r="W7" s="1">
-        <f t="shared" ref="W7:W70" si="6">(F7+O7+P7+Q7+R7)/S7</f>
+        <f t="shared" ref="W7:W70" si="7">(F7+O7+P7+Q7+R7)/S7</f>
         <v>60.770408460552396</v>
       </c>
       <c r="X7" s="1">
@@ -1649,10 +1644,13 @@
         <v>58</v>
       </c>
       <c r="AI7" s="1">
-        <f t="shared" ref="AI7:AI70" si="7">ROUND(G7*U7,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="1"/>
+        <f t="shared" ref="AI7:AI70" si="8">ROUND(G7*U7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="1">
+        <f t="shared" si="3"/>
+        <v>397.7769090909091</v>
+      </c>
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
       <c r="AM7" s="1"/>
@@ -1711,22 +1709,22 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>41.674400000000006</v>
       </c>
       <c r="T8" s="5"/>
       <c r="U8" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V8" s="1">
-        <f t="shared" si="5"/>
-        <v>21.298706160136678</v>
-      </c>
-      <c r="W8" s="1">
         <f t="shared" si="6"/>
         <v>21.298706160136678</v>
       </c>
+      <c r="W8" s="1">
+        <f t="shared" si="7"/>
+        <v>21.298706160136678</v>
+      </c>
       <c r="X8" s="1">
         <v>95.290599999999998</v>
       </c>
@@ -1759,10 +1757,13 @@
       </c>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="1">
+        <f t="shared" si="3"/>
+        <v>421.18872727272731</v>
+      </c>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
@@ -1807,22 +1808,22 @@
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
       <c r="S9" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T9" s="12"/>
       <c r="U9" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V9" s="1" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W9" s="10" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W9" s="10" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X9" s="10">
         <v>0</v>
       </c>
@@ -1857,10 +1858,13 @@
         <v>44</v>
       </c>
       <c r="AI9" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
@@ -1919,11 +1923,11 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>130.4</v>
       </c>
       <c r="T10" s="5">
-        <f t="shared" ref="T10:T16" si="8">12*S10-R10-Q10-P10-O10-F10</f>
+        <f t="shared" ref="T10:T16" si="9">12*S10-R10-Q10-P10-O10-F10</f>
         <v>365.57999999999993</v>
       </c>
       <c r="U10" s="5">
@@ -1931,11 +1935,11 @@
         <v>628.98799999999994</v>
       </c>
       <c r="V10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.02</v>
       </c>
       <c r="W10" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.1964723926380376</v>
       </c>
       <c r="X10" s="1">
@@ -1970,10 +1974,13 @@
       </c>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>283</v>
       </c>
-      <c r="AJ10" s="1"/>
+      <c r="AJ10" s="1">
+        <f t="shared" si="3"/>
+        <v>745.81818181818187</v>
+      </c>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1"/>
@@ -2032,22 +2039,22 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>95.2</v>
       </c>
       <c r="T11" s="5"/>
       <c r="U11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V11" s="1">
-        <f t="shared" si="5"/>
-        <v>14.118382352941177</v>
-      </c>
-      <c r="W11" s="1">
         <f t="shared" si="6"/>
         <v>14.118382352941177</v>
       </c>
+      <c r="W11" s="1">
+        <f t="shared" si="7"/>
+        <v>14.118382352941177</v>
+      </c>
       <c r="X11" s="1">
         <v>133.4</v>
       </c>
@@ -2080,10 +2087,13 @@
       </c>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="1">
+        <f t="shared" si="3"/>
+        <v>866.9818181818182</v>
+      </c>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
@@ -2142,22 +2152,22 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="T12" s="5"/>
       <c r="U12" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V12" s="1">
-        <f t="shared" si="5"/>
-        <v>12.947999999999999</v>
-      </c>
-      <c r="W12" s="1">
         <f t="shared" si="6"/>
         <v>12.947999999999999</v>
       </c>
+      <c r="W12" s="1">
+        <f t="shared" si="7"/>
+        <v>12.947999999999999</v>
+      </c>
       <c r="X12" s="1">
         <v>20.2</v>
       </c>
@@ -2190,10 +2200,13 @@
       </c>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="1">
+        <f t="shared" si="3"/>
+        <v>123.19999999999999</v>
+      </c>
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
@@ -2252,22 +2265,22 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13.6</v>
       </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V13" s="1">
-        <f t="shared" si="5"/>
-        <v>22.191176470588232</v>
-      </c>
-      <c r="W13" s="1">
         <f t="shared" si="6"/>
         <v>22.191176470588232</v>
       </c>
+      <c r="W13" s="1">
+        <f t="shared" si="7"/>
+        <v>22.191176470588232</v>
+      </c>
       <c r="X13" s="1">
         <v>30.4</v>
       </c>
@@ -2300,10 +2313,13 @@
       </c>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="1">
+        <f t="shared" si="3"/>
+        <v>159.59999999999997</v>
+      </c>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
@@ -2362,23 +2378,23 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28.6</v>
       </c>
       <c r="T14" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>57.910000000000053</v>
       </c>
       <c r="U14" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>57.910000000000053</v>
       </c>
       <c r="V14" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12.000000000000002</v>
       </c>
       <c r="W14" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.9751748251748236</v>
       </c>
       <c r="X14" s="1">
@@ -2413,10 +2429,13 @@
       </c>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="AJ14" s="1"/>
+      <c r="AJ14" s="1">
+        <f t="shared" si="3"/>
+        <v>168.63636363636363</v>
+      </c>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
@@ -2475,23 +2494,23 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101.03440000000001</v>
       </c>
       <c r="T15" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>229.76795000000004</v>
       </c>
       <c r="U15" s="5">
-        <f t="shared" ref="U15:U16" si="9">T15+$U$1*S15</f>
+        <f t="shared" ref="U15:U16" si="10">T15+$U$1*S15</f>
         <v>433.85743800000006</v>
       </c>
       <c r="V15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.020000000000001</v>
       </c>
       <c r="W15" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.7258443658793432</v>
       </c>
       <c r="X15" s="1">
@@ -2526,10 +2545,13 @@
       </c>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>434</v>
       </c>
-      <c r="AJ15" s="1"/>
+      <c r="AJ15" s="1">
+        <f t="shared" si="3"/>
+        <v>673.27387272727276</v>
+      </c>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
@@ -2588,23 +2610,23 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>485.00200000000007</v>
       </c>
       <c r="T16" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1783.9665999999995</v>
       </c>
       <c r="U16" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2763.6706399999998</v>
       </c>
       <c r="V16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.020000000000001</v>
       </c>
       <c r="W16" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.3217335186246668</v>
       </c>
       <c r="X16" s="1">
@@ -2639,10 +2661,13 @@
       </c>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2764</v>
       </c>
-      <c r="AJ16" s="1"/>
+      <c r="AJ16" s="1">
+        <f t="shared" si="3"/>
+        <v>3114.7580545454548</v>
+      </c>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
@@ -2701,22 +2726,22 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.6536</v>
       </c>
       <c r="T17" s="5"/>
       <c r="U17" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V17" s="1">
-        <f t="shared" si="5"/>
-        <v>25.266632695724894</v>
-      </c>
-      <c r="W17" s="1">
         <f t="shared" si="6"/>
         <v>25.266632695724894</v>
       </c>
+      <c r="W17" s="1">
+        <f t="shared" si="7"/>
+        <v>25.266632695724894</v>
+      </c>
       <c r="X17" s="1">
         <v>10.663399999999999</v>
       </c>
@@ -2749,10 +2774,13 @@
       </c>
       <c r="AH17" s="1"/>
       <c r="AI17" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="1">
+        <f t="shared" si="3"/>
+        <v>96.798545454545476</v>
+      </c>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
@@ -2809,20 +2837,20 @@
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
       <c r="S18" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.50919999999999999</v>
       </c>
       <c r="T18" s="12"/>
       <c r="U18" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W18" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X18" s="10">
@@ -2859,10 +2887,13 @@
         <v>56</v>
       </c>
       <c r="AI18" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="1">
+        <f t="shared" si="3"/>
+        <v>566.08274545454549</v>
+      </c>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
@@ -2921,22 +2952,22 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.9654000000000007</v>
       </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V19" s="1">
-        <f t="shared" si="5"/>
-        <v>13.089177105570545</v>
-      </c>
-      <c r="W19" s="1">
         <f t="shared" si="6"/>
         <v>13.089177105570545</v>
       </c>
+      <c r="W19" s="1">
+        <f t="shared" si="7"/>
+        <v>13.089177105570545</v>
+      </c>
       <c r="X19" s="1">
         <v>3.7240000000000002</v>
       </c>
@@ -2969,10 +3000,13 @@
       </c>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="1">
+        <f t="shared" si="3"/>
+        <v>53.92736363636363</v>
+      </c>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
@@ -3031,22 +3065,22 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.2141999999999999</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V20" s="1">
-        <f t="shared" si="5"/>
-        <v>12.419059370699063</v>
-      </c>
-      <c r="W20" s="1">
         <f t="shared" si="6"/>
         <v>12.419059370699063</v>
       </c>
+      <c r="W20" s="1">
+        <f t="shared" si="7"/>
+        <v>12.419059370699063</v>
+      </c>
       <c r="X20" s="1">
         <v>3.7368000000000001</v>
       </c>
@@ -3079,10 +3113,13 @@
       </c>
       <c r="AH20" s="1"/>
       <c r="AI20" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="1">
+        <f t="shared" si="3"/>
+        <v>21.661436363636366</v>
+      </c>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
@@ -3141,11 +3178,11 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>82.202399999999997</v>
       </c>
       <c r="T21" s="5">
-        <f t="shared" ref="T21" si="10">12*S21-R21-Q21-P21-O21-F21</f>
+        <f t="shared" ref="T21" si="11">12*S21-R21-Q21-P21-O21-F21</f>
         <v>172.85627999999991</v>
       </c>
       <c r="U21" s="5">
@@ -3153,11 +3190,11 @@
         <v>338.90512799999988</v>
       </c>
       <c r="V21" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.019999999999998</v>
       </c>
       <c r="W21" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.897186943446906</v>
       </c>
       <c r="X21" s="1">
@@ -3192,10 +3229,13 @@
       </c>
       <c r="AH21" s="1"/>
       <c r="AI21" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>339</v>
       </c>
-      <c r="AJ21" s="1"/>
+      <c r="AJ21" s="1">
+        <f t="shared" si="3"/>
+        <v>597.25616363636368</v>
+      </c>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
       <c r="AM21" s="1"/>
@@ -3248,22 +3288,22 @@
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
       <c r="S22" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T22" s="12"/>
       <c r="U22" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V22" s="1" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W22" s="10" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W22" s="10" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X22" s="10">
         <v>0</v>
       </c>
@@ -3296,10 +3336,13 @@
       </c>
       <c r="AH22" s="10"/>
       <c r="AI22" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="1">
+        <f t="shared" si="3"/>
+        <v>7.7336</v>
+      </c>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
       <c r="AM22" s="1"/>
@@ -3358,22 +3401,22 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19.5242</v>
       </c>
       <c r="T23" s="5"/>
       <c r="U23" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V23" s="1">
-        <f t="shared" si="5"/>
-        <v>12.678419602339661</v>
-      </c>
-      <c r="W23" s="1">
         <f t="shared" si="6"/>
         <v>12.678419602339661</v>
       </c>
+      <c r="W23" s="1">
+        <f t="shared" si="7"/>
+        <v>12.678419602339661</v>
+      </c>
       <c r="X23" s="1">
         <v>23.744399999999999</v>
       </c>
@@ -3406,10 +3449,13 @@
       </c>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="1">
+        <f t="shared" si="3"/>
+        <v>163.71778181818183</v>
+      </c>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
@@ -3468,23 +3514,23 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>38.613</v>
       </c>
       <c r="T24" s="5">
-        <f t="shared" ref="T24" si="11">12*S24-R24-Q24-P24-O24-F24</f>
+        <f t="shared" ref="T24" si="12">12*S24-R24-Q24-P24-O24-F24</f>
         <v>51.41640000000001</v>
       </c>
       <c r="U24" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>51.41640000000001</v>
       </c>
       <c r="V24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="W24" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10.668417372387538</v>
       </c>
       <c r="X24" s="1">
@@ -3519,10 +3565,13 @@
       </c>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>51</v>
       </c>
-      <c r="AJ24" s="1"/>
+      <c r="AJ24" s="1">
+        <f t="shared" si="3"/>
+        <v>267.14278181818179</v>
+      </c>
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
       <c r="AM24" s="1"/>
@@ -3581,7 +3630,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.9451999999999998</v>
       </c>
       <c r="T25" s="5">
@@ -3589,15 +3638,15 @@
         <v>46.570999999999998</v>
       </c>
       <c r="U25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>46.570999999999998</v>
       </c>
       <c r="V25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="W25" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.1666218125546659</v>
       </c>
       <c r="X25" s="1">
@@ -3632,10 +3681,13 @@
       </c>
       <c r="AH25" s="1"/>
       <c r="AI25" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>47</v>
       </c>
-      <c r="AJ25" s="1"/>
+      <c r="AJ25" s="1">
+        <f t="shared" si="3"/>
+        <v>25.753127272727273</v>
+      </c>
       <c r="AK25" s="1"/>
       <c r="AL25" s="1"/>
       <c r="AM25" s="1"/>
@@ -3694,22 +3746,22 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>38.692599999999999</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V26" s="1">
-        <f t="shared" si="5"/>
-        <v>16.997436202271235</v>
-      </c>
-      <c r="W26" s="1">
         <f t="shared" si="6"/>
         <v>16.997436202271235</v>
       </c>
+      <c r="W26" s="1">
+        <f t="shared" si="7"/>
+        <v>16.997436202271235</v>
+      </c>
       <c r="X26" s="1">
         <v>45.932200000000002</v>
       </c>
@@ -3740,14 +3792,17 @@
       <c r="AG26" s="1">
         <v>44.4452</v>
       </c>
-      <c r="AH26" s="14" t="s">
+      <c r="AH26" s="13" t="s">
         <v>67</v>
       </c>
       <c r="AI26" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="1">
+        <f t="shared" si="3"/>
+        <v>311.33709090909093</v>
+      </c>
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
@@ -3792,22 +3847,22 @@
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T27" s="12"/>
       <c r="U27" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V27" s="1" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W27" s="10" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W27" s="10" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X27" s="10">
         <v>0</v>
       </c>
@@ -3842,10 +3897,13 @@
         <v>44</v>
       </c>
       <c r="AI27" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="1">
+        <f>(S27+X27+Y27+Z27+AA27+AB27+AC27+AD27+AE27+AF27+AG27)/11*7</f>
+        <v>0</v>
+      </c>
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
       <c r="AM27" s="1"/>
@@ -3858,7 +3916,7 @@
       <c r="AT27" s="1"/>
     </row>
     <row r="28" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -3890,22 +3948,22 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V28" s="1" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W28" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="W28" s="1" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="X28" s="1">
         <v>0</v>
       </c>
@@ -3940,10 +3998,13 @@
         <v>70</v>
       </c>
       <c r="AI28" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="1">
+        <f t="shared" ref="AJ28:AJ91" si="13">(S28+X28+Y28+Z28+AA28+AB28+AC28+AD28+AE28+AF28+AG28)/11*7</f>
+        <v>0</v>
+      </c>
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
       <c r="AM28" s="1"/>
@@ -4002,23 +4063,23 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>38.505600000000001</v>
       </c>
       <c r="T29" s="5">
-        <f t="shared" ref="T29:T42" si="12">12*S29-R29-Q29-P29-O29-F29</f>
+        <f t="shared" ref="T29:T42" si="14">12*S29-R29-Q29-P29-O29-F29</f>
         <v>136.31720000000001</v>
       </c>
       <c r="U29" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>136.31720000000001</v>
       </c>
       <c r="V29" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="W29" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.4598084434471872</v>
       </c>
       <c r="X29" s="1">
@@ -4053,10 +4114,13 @@
       </c>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>136</v>
       </c>
-      <c r="AJ29" s="1"/>
+      <c r="AJ29" s="1">
+        <f t="shared" si="13"/>
+        <v>254.95616363636361</v>
+      </c>
       <c r="AK29" s="1"/>
       <c r="AL29" s="1"/>
       <c r="AM29" s="1"/>
@@ -4115,23 +4179,23 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.3886</v>
       </c>
       <c r="T30" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>66.767200000000031</v>
       </c>
       <c r="U30" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>66.767200000000031</v>
       </c>
       <c r="V30" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="W30" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9259973396141215</v>
       </c>
       <c r="X30" s="1">
@@ -4166,10 +4230,13 @@
       </c>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>67</v>
       </c>
-      <c r="AJ30" s="1"/>
+      <c r="AJ30" s="1">
+        <f t="shared" si="13"/>
+        <v>255.22305454545454</v>
+      </c>
       <c r="AK30" s="1"/>
       <c r="AL30" s="1"/>
       <c r="AM30" s="1"/>
@@ -4230,7 +4297,7 @@
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>290.73820000000001</v>
       </c>
       <c r="T31" s="5">
@@ -4241,11 +4308,11 @@
         <v>1700</v>
       </c>
       <c r="V31" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.8498890410685593</v>
       </c>
       <c r="W31" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.0027041854149163</v>
       </c>
       <c r="X31" s="1">
@@ -4280,10 +4347,13 @@
       </c>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1700</v>
       </c>
-      <c r="AJ31" s="1"/>
+      <c r="AJ31" s="1">
+        <f t="shared" si="13"/>
+        <v>1174.3802000000001</v>
+      </c>
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
       <c r="AM31" s="1"/>
@@ -4344,22 +4414,22 @@
       </c>
       <c r="R32" s="1"/>
       <c r="S32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.2767999999999997</v>
       </c>
       <c r="T32" s="5">
         <v>40</v>
       </c>
       <c r="U32" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="V32" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.3543056397816864</v>
       </c>
       <c r="W32" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-0.22604608853850788</v>
       </c>
       <c r="X32" s="1">
@@ -4394,10 +4464,13 @@
       </c>
       <c r="AH32" s="1"/>
       <c r="AI32" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="AJ32" s="1"/>
+      <c r="AJ32" s="1">
+        <f t="shared" si="13"/>
+        <v>7.3344727272727273</v>
+      </c>
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
       <c r="AM32" s="1"/>
@@ -4456,7 +4529,7 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19.0808</v>
       </c>
       <c r="T33" s="5">
@@ -4464,15 +4537,15 @@
         <v>133.51599999999999</v>
       </c>
       <c r="U33" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>133.51599999999999</v>
       </c>
       <c r="V33" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="W33" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.0025994717202624</v>
       </c>
       <c r="X33" s="1">
@@ -4507,10 +4580,13 @@
       </c>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>134</v>
       </c>
-      <c r="AJ33" s="1"/>
+      <c r="AJ33" s="1">
+        <f t="shared" si="13"/>
+        <v>106.86390909090909</v>
+      </c>
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
@@ -4569,22 +4645,22 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20.953200000000002</v>
       </c>
       <c r="T34" s="5"/>
       <c r="U34" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V34" s="1">
-        <f t="shared" si="5"/>
-        <v>17.143376668002976</v>
-      </c>
-      <c r="W34" s="1">
         <f t="shared" si="6"/>
         <v>17.143376668002976</v>
       </c>
+      <c r="W34" s="1">
+        <f t="shared" si="7"/>
+        <v>17.143376668002976</v>
+      </c>
       <c r="X34" s="1">
         <v>32.764400000000002</v>
       </c>
@@ -4617,10 +4693,13 @@
       </c>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="1">
+        <f t="shared" si="13"/>
+        <v>166.57250909090914</v>
+      </c>
       <c r="AK34" s="1"/>
       <c r="AL34" s="1"/>
       <c r="AM34" s="1"/>
@@ -4679,22 +4758,22 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.8666</v>
       </c>
       <c r="T35" s="5"/>
       <c r="U35" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V35" s="1">
-        <f t="shared" si="5"/>
-        <v>29.849998728802785</v>
-      </c>
-      <c r="W35" s="1">
         <f t="shared" si="6"/>
         <v>29.849998728802785</v>
       </c>
+      <c r="W35" s="1">
+        <f t="shared" si="7"/>
+        <v>29.849998728802785</v>
+      </c>
       <c r="X35" s="1">
         <v>12.2232</v>
       </c>
@@ -4727,10 +4806,13 @@
       </c>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="1">
+        <f t="shared" si="13"/>
+        <v>94.729854545454543</v>
+      </c>
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
       <c r="AM35" s="1"/>
@@ -4791,7 +4873,7 @@
       </c>
       <c r="R36" s="1"/>
       <c r="S36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>363</v>
       </c>
       <c r="T36" s="5">
@@ -4803,11 +4885,11 @@
         <v>1786.5055999999995</v>
       </c>
       <c r="V36" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.999999999999998</v>
       </c>
       <c r="W36" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.0784969696969702</v>
       </c>
       <c r="X36" s="1">
@@ -4842,10 +4924,13 @@
       </c>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>715</v>
       </c>
-      <c r="AJ36" s="1"/>
+      <c r="AJ36" s="1">
+        <f t="shared" si="13"/>
+        <v>2311.5310909090904</v>
+      </c>
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
       <c r="AM36" s="1"/>
@@ -4904,22 +4989,22 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>66.8</v>
       </c>
       <c r="T37" s="5"/>
       <c r="U37" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V37" s="1">
-        <f t="shared" si="5"/>
-        <v>12.074850299401197</v>
-      </c>
-      <c r="W37" s="1">
         <f t="shared" si="6"/>
         <v>12.074850299401197</v>
       </c>
+      <c r="W37" s="1">
+        <f t="shared" si="7"/>
+        <v>12.074850299401197</v>
+      </c>
       <c r="X37" s="1">
         <v>81</v>
       </c>
@@ -4952,10 +5037,13 @@
       </c>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="1">
+        <f t="shared" si="13"/>
+        <v>427.12727272727278</v>
+      </c>
       <c r="AK37" s="1"/>
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
@@ -5000,7 +5088,7 @@
         <v>715</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="15">E38-K38</f>
         <v>-45</v>
       </c>
       <c r="M38" s="1"/>
@@ -5014,11 +5102,11 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>134</v>
       </c>
       <c r="T38" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>539.73000000000025</v>
       </c>
       <c r="U38" s="5">
@@ -5026,11 +5114,11 @@
         <v>810.41000000000031</v>
       </c>
       <c r="V38" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.020000000000001</v>
       </c>
       <c r="W38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.9721641791044755</v>
       </c>
       <c r="X38" s="1">
@@ -5065,10 +5153,13 @@
       </c>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>324</v>
       </c>
-      <c r="AJ38" s="1"/>
+      <c r="AJ38" s="1">
+        <f t="shared" si="13"/>
+        <v>894.85454545454547</v>
+      </c>
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
       <c r="AM38" s="1"/>
@@ -5113,7 +5204,7 @@
         <v>156</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-26</v>
       </c>
       <c r="M39" s="1"/>
@@ -5127,23 +5218,23 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>168</v>
       </c>
       <c r="V39" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="W39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.5384615384615383</v>
       </c>
       <c r="X39" s="1">
@@ -5178,10 +5269,13 @@
       </c>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>67</v>
       </c>
-      <c r="AJ39" s="1"/>
+      <c r="AJ39" s="1">
+        <f t="shared" si="13"/>
+        <v>112.25454545454548</v>
+      </c>
       <c r="AK39" s="1"/>
       <c r="AL39" s="1"/>
       <c r="AM39" s="1"/>
@@ -5226,7 +5320,7 @@
         <v>19.8</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-10.148000000000001</v>
       </c>
       <c r="M40" s="1"/>
@@ -5240,22 +5334,22 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9303999999999999</v>
       </c>
       <c r="T40" s="5"/>
       <c r="U40" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V40" s="1">
-        <f t="shared" si="5"/>
-        <v>41.24093452134273</v>
-      </c>
-      <c r="W40" s="1">
         <f t="shared" si="6"/>
         <v>41.24093452134273</v>
       </c>
+      <c r="W40" s="1">
+        <f t="shared" si="7"/>
+        <v>41.24093452134273</v>
+      </c>
       <c r="X40" s="1">
         <v>2.2482000000000002</v>
       </c>
@@ -5288,10 +5382,13 @@
       </c>
       <c r="AH40" s="1"/>
       <c r="AI40" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="1">
+        <f t="shared" si="13"/>
+        <v>23.574727272727277</v>
+      </c>
       <c r="AK40" s="1"/>
       <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
@@ -5336,7 +5433,7 @@
         <v>118</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-1</v>
       </c>
       <c r="M41" s="1"/>
@@ -5350,23 +5447,23 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23.4</v>
       </c>
       <c r="T41" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>8.3999999999999488</v>
       </c>
       <c r="U41" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.3999999999999488</v>
       </c>
       <c r="V41" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.999999999999998</v>
       </c>
       <c r="W41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.641025641025641</v>
       </c>
       <c r="X41" s="1">
@@ -5401,10 +5498,13 @@
       </c>
       <c r="AH41" s="1"/>
       <c r="AI41" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AJ41" s="1"/>
+      <c r="AJ41" s="1">
+        <f t="shared" si="13"/>
+        <v>100.54545454545455</v>
+      </c>
       <c r="AK41" s="1"/>
       <c r="AL41" s="1"/>
       <c r="AM41" s="1"/>
@@ -5449,7 +5549,7 @@
         <v>174</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-9</v>
       </c>
       <c r="M42" s="1"/>
@@ -5463,23 +5563,23 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>33</v>
       </c>
       <c r="T42" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>247</v>
       </c>
       <c r="U42" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>247</v>
       </c>
       <c r="V42" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="W42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5151515151515156</v>
       </c>
       <c r="X42" s="1">
@@ -5514,10 +5614,13 @@
       </c>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>86</v>
       </c>
-      <c r="AJ42" s="1"/>
+      <c r="AJ42" s="1">
+        <f t="shared" si="13"/>
+        <v>111.74545454545454</v>
+      </c>
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
       <c r="AM42" s="1"/>
@@ -5562,7 +5665,7 @@
         <v>6.8</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-7.5</v>
       </c>
       <c r="M43" s="1"/>
@@ -5576,22 +5679,22 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.13999999999999999</v>
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V43" s="1">
-        <f t="shared" si="5"/>
-        <v>-829.79142857142881</v>
-      </c>
-      <c r="W43" s="1">
         <f t="shared" si="6"/>
         <v>-829.79142857142881</v>
       </c>
+      <c r="W43" s="1">
+        <f t="shared" si="7"/>
+        <v>-829.79142857142881</v>
+      </c>
       <c r="X43" s="1">
         <v>1.7484</v>
       </c>
@@ -5624,10 +5727,13 @@
       </c>
       <c r="AH43" s="1"/>
       <c r="AI43" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="1">
+        <f t="shared" si="13"/>
+        <v>37.739927272727272</v>
+      </c>
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
       <c r="AM43" s="1"/>
@@ -5672,7 +5778,7 @@
         <v>28</v>
       </c>
       <c r="L44" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-5</v>
       </c>
       <c r="M44" s="10"/>
@@ -5686,22 +5792,22 @@
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
       <c r="S44" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="T44" s="12"/>
       <c r="U44" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V44" s="1">
-        <f t="shared" si="5"/>
-        <v>16.304347826086957</v>
-      </c>
-      <c r="W44" s="10">
         <f t="shared" si="6"/>
         <v>16.304347826086957</v>
       </c>
+      <c r="W44" s="10">
+        <f t="shared" si="7"/>
+        <v>16.304347826086957</v>
+      </c>
       <c r="X44" s="10">
         <v>4.5999999999999996</v>
       </c>
@@ -5734,10 +5840,13 @@
       </c>
       <c r="AH44" s="10"/>
       <c r="AI44" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ44" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="1">
+        <f t="shared" si="13"/>
+        <v>50.909090909090907</v>
+      </c>
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
       <c r="AM44" s="1"/>
@@ -5782,7 +5891,7 @@
         <v>252</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-158</v>
       </c>
       <c r="M45" s="1"/>
@@ -5796,22 +5905,22 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18.8</v>
       </c>
       <c r="T45" s="5"/>
       <c r="U45" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V45" s="1">
-        <f t="shared" si="5"/>
-        <v>14.566489361702128</v>
-      </c>
-      <c r="W45" s="1">
         <f t="shared" si="6"/>
         <v>14.566489361702128</v>
       </c>
+      <c r="W45" s="1">
+        <f t="shared" si="7"/>
+        <v>14.566489361702128</v>
+      </c>
       <c r="X45" s="1">
         <v>25.6</v>
       </c>
@@ -5844,10 +5953,13 @@
       </c>
       <c r="AH45" s="1"/>
       <c r="AI45" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ45" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="1">
+        <f t="shared" si="13"/>
+        <v>212.03636363636363</v>
+      </c>
       <c r="AK45" s="1"/>
       <c r="AL45" s="1"/>
       <c r="AM45" s="1"/>
@@ -5892,7 +6004,7 @@
         <v>302</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-35</v>
       </c>
       <c r="M46" s="1"/>
@@ -5908,7 +6020,7 @@
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>53.4</v>
       </c>
       <c r="T46" s="5">
@@ -5919,11 +6031,11 @@
         <v>400</v>
       </c>
       <c r="V46" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.2247191011235952</v>
       </c>
       <c r="W46" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.73408239700374511</v>
       </c>
       <c r="X46" s="1">
@@ -5958,10 +6070,13 @@
       </c>
       <c r="AH46" s="1"/>
       <c r="AI46" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>160</v>
       </c>
-      <c r="AJ46" s="1"/>
+      <c r="AJ46" s="1">
+        <f t="shared" si="13"/>
+        <v>236.47272727272727</v>
+      </c>
       <c r="AK46" s="1"/>
       <c r="AL46" s="1"/>
       <c r="AM46" s="1"/>
@@ -6006,7 +6121,7 @@
         <v>144.30000000000001</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-44.796000000000006</v>
       </c>
       <c r="M47" s="1"/>
@@ -6020,22 +6135,22 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19.9008</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V47" s="1">
-        <f t="shared" si="5"/>
-        <v>13.060660877954655</v>
-      </c>
-      <c r="W47" s="1">
         <f t="shared" si="6"/>
         <v>13.060660877954655</v>
       </c>
+      <c r="W47" s="1">
+        <f t="shared" si="7"/>
+        <v>13.060660877954655</v>
+      </c>
       <c r="X47" s="1">
         <v>25.02</v>
       </c>
@@ -6068,10 +6183,13 @@
       </c>
       <c r="AH47" s="1"/>
       <c r="AI47" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="1">
+        <f t="shared" si="13"/>
+        <v>134.83909090909094</v>
+      </c>
       <c r="AK47" s="1"/>
       <c r="AL47" s="1"/>
       <c r="AM47" s="1"/>
@@ -6116,7 +6234,7 @@
         <v>358</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-30</v>
       </c>
       <c r="M48" s="1"/>
@@ -6130,11 +6248,11 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>65.599999999999994</v>
       </c>
       <c r="T48" s="5">
-        <f t="shared" ref="T48:T69" si="14">12*S48-R48-Q48-P48-O48-F48</f>
+        <f t="shared" ref="T48:T69" si="16">12*S48-R48-Q48-P48-O48-F48</f>
         <v>392.59999999999991</v>
       </c>
       <c r="U48" s="5">
@@ -6142,11 +6260,11 @@
         <v>525.11199999999985</v>
       </c>
       <c r="V48" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.02</v>
       </c>
       <c r="W48" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.0152439024390256</v>
       </c>
       <c r="X48" s="1">
@@ -6181,10 +6299,13 @@
       </c>
       <c r="AH48" s="1"/>
       <c r="AI48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>184</v>
       </c>
-      <c r="AJ48" s="1"/>
+      <c r="AJ48" s="1">
+        <f t="shared" si="13"/>
+        <v>345.92727272727274</v>
+      </c>
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
       <c r="AM48" s="1"/>
@@ -6229,7 +6350,7 @@
         <v>283</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-255</v>
       </c>
       <c r="M49" s="1"/>
@@ -6243,22 +6364,22 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.6</v>
       </c>
       <c r="T49" s="5">
         <v>200</v>
       </c>
       <c r="U49" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>200</v>
       </c>
       <c r="V49" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>82.679714285714311</v>
       </c>
       <c r="W49" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>46.965428571428589</v>
       </c>
       <c r="X49" s="1">
@@ -6293,10 +6414,13 @@
       </c>
       <c r="AH49" s="1"/>
       <c r="AI49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
-      <c r="AJ49" s="1"/>
+      <c r="AJ49" s="1">
+        <f t="shared" si="13"/>
+        <v>407.02174545454545</v>
+      </c>
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
       <c r="AM49" s="1"/>
@@ -6341,7 +6465,7 @@
         <v>94.9</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-27.454000000000008</v>
       </c>
       <c r="M50" s="1"/>
@@ -6355,22 +6479,22 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13.4892</v>
       </c>
       <c r="T50" s="5"/>
       <c r="U50" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V50" s="1">
-        <f t="shared" si="5"/>
-        <v>15.975795451175756</v>
-      </c>
-      <c r="W50" s="1">
         <f t="shared" si="6"/>
         <v>15.975795451175756</v>
       </c>
+      <c r="W50" s="1">
+        <f t="shared" si="7"/>
+        <v>15.975795451175756</v>
+      </c>
       <c r="X50" s="1">
         <v>18.758400000000002</v>
       </c>
@@ -6403,10 +6527,13 @@
       </c>
       <c r="AH50" s="1"/>
       <c r="AI50" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ50" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="1">
+        <f t="shared" si="13"/>
+        <v>120.98049090909092</v>
+      </c>
       <c r="AK50" s="1"/>
       <c r="AL50" s="1"/>
       <c r="AM50" s="1"/>
@@ -6451,7 +6578,7 @@
         <v>166.4</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-19.637</v>
       </c>
       <c r="M51" s="1"/>
@@ -6465,22 +6592,22 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.352600000000002</v>
       </c>
       <c r="T51" s="5"/>
       <c r="U51" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V51" s="1">
-        <f t="shared" si="5"/>
-        <v>14.984635091950969</v>
-      </c>
-      <c r="W51" s="1">
         <f t="shared" si="6"/>
         <v>14.984635091950969</v>
       </c>
+      <c r="W51" s="1">
+        <f t="shared" si="7"/>
+        <v>14.984635091950969</v>
+      </c>
       <c r="X51" s="1">
         <v>27.397400000000001</v>
       </c>
@@ -6511,14 +6638,17 @@
       <c r="AG51" s="1">
         <v>28.571000000000002</v>
       </c>
-      <c r="AH51" s="14" t="s">
+      <c r="AH51" s="13" t="s">
         <v>67</v>
       </c>
       <c r="AI51" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="1">
+        <f t="shared" si="13"/>
+        <v>201.66796363636365</v>
+      </c>
       <c r="AK51" s="1"/>
       <c r="AL51" s="1"/>
       <c r="AM51" s="1"/>
@@ -6563,7 +6693,7 @@
         <v>204.9</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1.3439999999999941</v>
       </c>
       <c r="M52" s="1"/>
@@ -6579,7 +6709,7 @@
       </c>
       <c r="R52" s="1"/>
       <c r="S52" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>41.248800000000003</v>
       </c>
       <c r="T52" s="5">
@@ -6590,11 +6720,11 @@
         <v>250</v>
       </c>
       <c r="V52" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.9153623862997211</v>
       </c>
       <c r="W52" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.8545800120245919</v>
       </c>
       <c r="X52" s="1">
@@ -6629,10 +6759,13 @@
       </c>
       <c r="AH52" s="1"/>
       <c r="AI52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
-      <c r="AJ52" s="1"/>
+      <c r="AJ52" s="1">
+        <f t="shared" si="13"/>
+        <v>162.47649090909093</v>
+      </c>
       <c r="AK52" s="1"/>
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
@@ -6677,7 +6810,7 @@
         <v>130</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-26</v>
       </c>
       <c r="M53" s="1"/>
@@ -6691,22 +6824,22 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20.8</v>
       </c>
       <c r="T53" s="5"/>
       <c r="U53" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V53" s="1">
-        <f t="shared" si="5"/>
-        <v>19.840384615384615</v>
-      </c>
-      <c r="W53" s="1">
         <f t="shared" si="6"/>
         <v>19.840384615384615</v>
       </c>
+      <c r="W53" s="1">
+        <f t="shared" si="7"/>
+        <v>19.840384615384615</v>
+      </c>
       <c r="X53" s="1">
         <v>35.4</v>
       </c>
@@ -6739,10 +6872,13 @@
       </c>
       <c r="AH53" s="1"/>
       <c r="AI53" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ53" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="1">
+        <f t="shared" si="13"/>
+        <v>211.27272727272728</v>
+      </c>
       <c r="AK53" s="1"/>
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
@@ -6787,7 +6923,7 @@
         <v>284</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-92</v>
       </c>
       <c r="M54" s="1"/>
@@ -6801,22 +6937,22 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>38.4</v>
       </c>
       <c r="T54" s="5"/>
       <c r="U54" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V54" s="1">
-        <f t="shared" si="5"/>
-        <v>13.453645833333335</v>
-      </c>
-      <c r="W54" s="1">
         <f t="shared" si="6"/>
         <v>13.453645833333335</v>
       </c>
+      <c r="W54" s="1">
+        <f t="shared" si="7"/>
+        <v>13.453645833333335</v>
+      </c>
       <c r="X54" s="1">
         <v>47.2</v>
       </c>
@@ -6849,10 +6985,13 @@
       </c>
       <c r="AH54" s="1"/>
       <c r="AI54" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ54" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="1">
+        <f t="shared" si="13"/>
+        <v>370.74545454545449</v>
+      </c>
       <c r="AK54" s="1"/>
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
@@ -6897,7 +7036,7 @@
         <v>48</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-6</v>
       </c>
       <c r="M55" s="1"/>
@@ -6913,22 +7052,22 @@
       </c>
       <c r="R55" s="1"/>
       <c r="S55" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.4</v>
       </c>
       <c r="T55" s="5">
         <v>48</v>
       </c>
       <c r="U55" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="V55" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.8571428571428577</v>
       </c>
       <c r="W55" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.1428571428571432</v>
       </c>
       <c r="X55" s="1">
@@ -6963,10 +7102,13 @@
       </c>
       <c r="AH55" s="1"/>
       <c r="AI55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="AJ55" s="1"/>
+      <c r="AJ55" s="1">
+        <f t="shared" si="13"/>
+        <v>20.236363636363642</v>
+      </c>
       <c r="AK55" s="1"/>
       <c r="AL55" s="1"/>
       <c r="AM55" s="1"/>
@@ -7011,7 +7153,7 @@
         <v>63</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-16</v>
       </c>
       <c r="M56" s="1"/>
@@ -7025,23 +7167,23 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.4</v>
       </c>
       <c r="T56" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>15.800000000000011</v>
       </c>
       <c r="U56" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15.800000000000011</v>
       </c>
       <c r="V56" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="W56" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10.319148936170212</v>
       </c>
       <c r="X56" s="1">
@@ -7076,10 +7218,13 @@
       </c>
       <c r="AH56" s="1"/>
       <c r="AI56" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="AJ56" s="1"/>
+      <c r="AJ56" s="1">
+        <f t="shared" si="13"/>
+        <v>63.890909090909091</v>
+      </c>
       <c r="AK56" s="1"/>
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
@@ -7124,7 +7269,7 @@
         <v>83.8</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-11.796999999999997</v>
       </c>
       <c r="M57" s="1"/>
@@ -7138,22 +7283,22 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14.400600000000001</v>
       </c>
       <c r="T57" s="5"/>
       <c r="U57" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V57" s="1">
-        <f t="shared" si="5"/>
-        <v>13.461244670360957</v>
-      </c>
-      <c r="W57" s="1">
         <f t="shared" si="6"/>
         <v>13.461244670360957</v>
       </c>
+      <c r="W57" s="1">
+        <f t="shared" si="7"/>
+        <v>13.461244670360957</v>
+      </c>
       <c r="X57" s="1">
         <v>10.9184</v>
       </c>
@@ -7188,10 +7333,13 @@
         <v>58</v>
       </c>
       <c r="AI57" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="1">
+        <f t="shared" si="13"/>
+        <v>90.072563636363626</v>
+      </c>
       <c r="AK57" s="1"/>
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
@@ -7236,7 +7384,7 @@
         <v>45</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-6</v>
       </c>
       <c r="M58" s="1"/>
@@ -7250,22 +7398,22 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.8</v>
       </c>
       <c r="T58" s="5"/>
       <c r="U58" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V58" s="1">
-        <f t="shared" si="5"/>
-        <v>31.53846153846154</v>
-      </c>
-      <c r="W58" s="1">
         <f t="shared" si="6"/>
         <v>31.53846153846154</v>
       </c>
+      <c r="W58" s="1">
+        <f t="shared" si="7"/>
+        <v>31.53846153846154</v>
+      </c>
       <c r="X58" s="1">
         <v>11</v>
       </c>
@@ -7296,14 +7444,17 @@
       <c r="AG58" s="1">
         <v>10.4</v>
       </c>
-      <c r="AH58" s="14" t="s">
+      <c r="AH58" s="13" t="s">
         <v>67</v>
       </c>
       <c r="AI58" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ58" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="1">
+        <f t="shared" si="13"/>
+        <v>77.509090909090901</v>
+      </c>
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
@@ -7348,7 +7499,7 @@
         <v>169.322</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>8.1610000000000014</v>
       </c>
       <c r="M59" s="1"/>
@@ -7362,23 +7513,23 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>35.496600000000001</v>
       </c>
       <c r="T59" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>98.677000000000049</v>
       </c>
       <c r="U59" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>98.677000000000049</v>
       </c>
       <c r="V59" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="W59" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.2200999532349552</v>
       </c>
       <c r="X59" s="1">
@@ -7413,10 +7564,13 @@
       </c>
       <c r="AH59" s="1"/>
       <c r="AI59" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>99</v>
       </c>
-      <c r="AJ59" s="1"/>
+      <c r="AJ59" s="1">
+        <f t="shared" si="13"/>
+        <v>221.80174545454548</v>
+      </c>
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
@@ -7461,7 +7615,7 @@
         <v>41.1</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>5.4709999999999965</v>
       </c>
       <c r="M60" s="1"/>
@@ -7475,23 +7629,23 @@
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
       <c r="S60" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.3141999999999996</v>
       </c>
       <c r="T60" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>42.642399999999995</v>
       </c>
       <c r="U60" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>42.642399999999995</v>
       </c>
       <c r="V60" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="W60" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.4217860900560435</v>
       </c>
       <c r="X60" s="1">
@@ -7526,10 +7680,13 @@
       </c>
       <c r="AH60" s="1"/>
       <c r="AI60" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>43</v>
       </c>
-      <c r="AJ60" s="1"/>
+      <c r="AJ60" s="1">
+        <f t="shared" si="13"/>
+        <v>47.727654545454541</v>
+      </c>
       <c r="AK60" s="1"/>
       <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
@@ -7574,7 +7731,7 @@
         <v>58</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-4</v>
       </c>
       <c r="M61" s="1"/>
@@ -7588,22 +7745,22 @@
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.8</v>
       </c>
       <c r="T61" s="5"/>
       <c r="U61" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V61" s="1">
-        <f t="shared" si="5"/>
-        <v>14.351851851851851</v>
-      </c>
-      <c r="W61" s="1">
         <f t="shared" si="6"/>
         <v>14.351851851851851</v>
       </c>
+      <c r="W61" s="1">
+        <f t="shared" si="7"/>
+        <v>14.351851851851851</v>
+      </c>
       <c r="X61" s="1">
         <v>12.8</v>
       </c>
@@ -7636,10 +7793,13 @@
       </c>
       <c r="AH61" s="1"/>
       <c r="AI61" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="1">
+        <f t="shared" si="13"/>
+        <v>66.563636363636363</v>
+      </c>
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
@@ -7684,7 +7844,7 @@
         <v>16</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-12</v>
       </c>
       <c r="M62" s="1"/>
@@ -7698,22 +7858,22 @@
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
       <c r="T62" s="5"/>
       <c r="U62" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V62" s="1">
-        <f t="shared" si="5"/>
-        <v>21.25</v>
-      </c>
-      <c r="W62" s="1">
         <f t="shared" si="6"/>
         <v>21.25</v>
       </c>
+      <c r="W62" s="1">
+        <f t="shared" si="7"/>
+        <v>21.25</v>
+      </c>
       <c r="X62" s="1">
         <v>0.8</v>
       </c>
@@ -7744,14 +7904,17 @@
       <c r="AG62" s="1">
         <v>3.6</v>
       </c>
-      <c r="AH62" s="14" t="s">
+      <c r="AH62" s="13" t="s">
         <v>67</v>
       </c>
       <c r="AI62" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ62" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="1">
+        <f t="shared" si="13"/>
+        <v>15.654545454545454</v>
+      </c>
       <c r="AK62" s="1"/>
       <c r="AL62" s="1"/>
       <c r="AM62" s="1"/>
@@ -7796,7 +7959,7 @@
         <v>99.4</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-12.913000000000011</v>
       </c>
       <c r="M63" s="1"/>
@@ -7810,23 +7973,23 @@
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
       <c r="S63" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.2974</v>
       </c>
       <c r="T63" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>62.483800000000002</v>
       </c>
       <c r="U63" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>62.483800000000002</v>
       </c>
       <c r="V63" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="W63" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.3876767606692333</v>
       </c>
       <c r="X63" s="1">
@@ -7861,10 +8024,13 @@
       </c>
       <c r="AH63" s="1"/>
       <c r="AI63" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>62</v>
       </c>
-      <c r="AJ63" s="1"/>
+      <c r="AJ63" s="1">
+        <f t="shared" si="13"/>
+        <v>84.627709090909093</v>
+      </c>
       <c r="AK63" s="1"/>
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
@@ -7909,7 +8075,7 @@
         <v>49.1</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-12.533000000000001</v>
       </c>
       <c r="M64" s="1"/>
@@ -7923,23 +8089,23 @@
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
       <c r="S64" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.3133999999999997</v>
       </c>
       <c r="T64" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>7.124799999999988</v>
       </c>
       <c r="U64" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.124799999999988</v>
       </c>
       <c r="V64" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.999999999999998</v>
       </c>
       <c r="W64" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.025788279049417</v>
       </c>
       <c r="X64" s="1">
@@ -7974,10 +8140,13 @@
       </c>
       <c r="AH64" s="1"/>
       <c r="AI64" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="AJ64" s="1"/>
+      <c r="AJ64" s="1">
+        <f t="shared" si="13"/>
+        <v>30.514781818181824</v>
+      </c>
       <c r="AK64" s="1"/>
       <c r="AL64" s="1"/>
       <c r="AM64" s="1"/>
@@ -8022,7 +8191,7 @@
         <v>510</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-47</v>
       </c>
       <c r="M65" s="1"/>
@@ -8036,23 +8205,23 @@
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
       <c r="S65" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>92.6</v>
       </c>
       <c r="T65" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>198.19999999999982</v>
       </c>
       <c r="U65" s="5">
-        <f t="shared" ref="U65" si="15">T65+$U$1*S65</f>
+        <f t="shared" ref="U65" si="17">T65+$U$1*S65</f>
         <v>385.25199999999984</v>
       </c>
       <c r="V65" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.02</v>
       </c>
       <c r="W65" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.8596112311015123</v>
       </c>
       <c r="X65" s="1">
@@ -8087,10 +8256,13 @@
       </c>
       <c r="AH65" s="1"/>
       <c r="AI65" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>154</v>
       </c>
-      <c r="AJ65" s="1"/>
+      <c r="AJ65" s="1">
+        <f t="shared" si="13"/>
+        <v>420.25454545454545</v>
+      </c>
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
       <c r="AM65" s="1"/>
@@ -8135,7 +8307,7 @@
         <v>366</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-35</v>
       </c>
       <c r="M66" s="1"/>
@@ -8151,7 +8323,7 @@
       </c>
       <c r="R66" s="1"/>
       <c r="S66" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>66.2</v>
       </c>
       <c r="T66" s="5">
@@ -8163,11 +8335,11 @@
         <v>491.20000000000016</v>
       </c>
       <c r="V66" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="W66" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.5800604229607242</v>
       </c>
       <c r="X66" s="1">
@@ -8202,10 +8374,13 @@
       </c>
       <c r="AH66" s="1"/>
       <c r="AI66" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>196</v>
       </c>
-      <c r="AJ66" s="1"/>
+      <c r="AJ66" s="1">
+        <f t="shared" si="13"/>
+        <v>441.76363636363641</v>
+      </c>
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
       <c r="AM66" s="1"/>
@@ -8250,7 +8425,7 @@
         <v>137.1</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.4879999999999995</v>
       </c>
       <c r="M67" s="1"/>
@@ -8264,22 +8439,22 @@
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
       <c r="S67" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>27.9176</v>
       </c>
       <c r="T67" s="5"/>
       <c r="U67" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V67" s="1">
-        <f t="shared" si="5"/>
-        <v>12.125948863799183</v>
-      </c>
-      <c r="W67" s="1">
         <f t="shared" si="6"/>
         <v>12.125948863799183</v>
       </c>
+      <c r="W67" s="1">
+        <f t="shared" si="7"/>
+        <v>12.125948863799183</v>
+      </c>
       <c r="X67" s="1">
         <v>32.401799999999987</v>
       </c>
@@ -8312,10 +8487,13 @@
       </c>
       <c r="AH67" s="1"/>
       <c r="AI67" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ67" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="1">
+        <f t="shared" si="13"/>
+        <v>206.78127272727272</v>
+      </c>
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
       <c r="AM67" s="1"/>
@@ -8360,7 +8538,7 @@
         <v>181.1</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-4.9569999999999936</v>
       </c>
       <c r="M68" s="1"/>
@@ -8374,23 +8552,23 @@
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
       <c r="S68" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>35.2286</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>229.19019999999983</v>
       </c>
       <c r="U68" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>229.19019999999983</v>
       </c>
       <c r="V68" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.999999999999998</v>
       </c>
       <c r="W68" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.4942007346303887</v>
       </c>
       <c r="X68" s="1">
@@ -8425,10 +8603,13 @@
       </c>
       <c r="AH68" s="1"/>
       <c r="AI68" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>229</v>
       </c>
-      <c r="AJ68" s="1"/>
+      <c r="AJ68" s="1">
+        <f t="shared" si="13"/>
+        <v>202.40398181818179</v>
+      </c>
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
       <c r="AM68" s="1"/>
@@ -8473,7 +8654,7 @@
         <v>364.53800000000001</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>-24.293999999999983</v>
       </c>
       <c r="M69" s="1"/>
@@ -8487,11 +8668,11 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
       <c r="S69" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>68.0488</v>
       </c>
       <c r="T69" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>215.43975999999975</v>
       </c>
       <c r="U69" s="5">
@@ -8499,11 +8680,11 @@
         <v>352.89833599999974</v>
       </c>
       <c r="V69" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>14.02</v>
       </c>
       <c r="W69" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.8340402769777029</v>
       </c>
       <c r="X69" s="1">
@@ -8538,10 +8719,13 @@
       </c>
       <c r="AH69" s="1"/>
       <c r="AI69" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>353</v>
       </c>
-      <c r="AJ69" s="1"/>
+      <c r="AJ69" s="1">
+        <f t="shared" si="13"/>
+        <v>528.61569090909097</v>
+      </c>
       <c r="AK69" s="1"/>
       <c r="AL69" s="1"/>
       <c r="AM69" s="1"/>
@@ -8586,7 +8770,7 @@
         <v>279.5</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="16">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="18">E70-K70</f>
         <v>-90.61099999999999</v>
       </c>
       <c r="M70" s="1"/>
@@ -8600,22 +8784,22 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>37.777799999999999</v>
       </c>
       <c r="T70" s="5"/>
       <c r="U70" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V70" s="1">
-        <f t="shared" si="5"/>
-        <v>15.689050182911659</v>
-      </c>
-      <c r="W70" s="1">
         <f t="shared" si="6"/>
         <v>15.689050182911659</v>
       </c>
+      <c r="W70" s="1">
+        <f t="shared" si="7"/>
+        <v>15.689050182911659</v>
+      </c>
       <c r="X70" s="1">
         <v>58.898200000000003</v>
       </c>
@@ -8648,10 +8832,13 @@
       </c>
       <c r="AH70" s="1"/>
       <c r="AI70" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AJ70" s="1"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="1">
+        <f t="shared" si="13"/>
+        <v>262.96174545454551</v>
+      </c>
       <c r="AK70" s="1"/>
       <c r="AL70" s="1"/>
       <c r="AM70" s="1"/>
@@ -8684,7 +8871,7 @@
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
       <c r="L71" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M71" s="10"/>
@@ -8696,20 +8883,20 @@
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
       <c r="S71" s="10">
-        <f t="shared" ref="S71:S131" si="17">E71/5</f>
+        <f t="shared" ref="S71:S131" si="19">E71/5</f>
         <v>0</v>
       </c>
       <c r="T71" s="12"/>
       <c r="U71" s="5">
-        <f t="shared" ref="U71:U131" si="18">T71</f>
+        <f t="shared" ref="U71:U131" si="20">T71</f>
         <v>0</v>
       </c>
       <c r="V71" s="1" t="e">
-        <f t="shared" ref="V71:V131" si="19">(F71+O71+P71+Q71+R71+U71)/S71</f>
+        <f t="shared" ref="V71:V131" si="21">(F71+O71+P71+Q71+R71+U71)/S71</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W71" s="10" t="e">
-        <f t="shared" ref="W71:W131" si="20">(F71+O71+P71+Q71+R71)/S71</f>
+        <f t="shared" ref="W71:W131" si="22">(F71+O71+P71+Q71+R71)/S71</f>
         <v>#DIV/0!</v>
       </c>
       <c r="X71" s="10">
@@ -8746,10 +8933,13 @@
         <v>44</v>
       </c>
       <c r="AI71" s="1">
-        <f t="shared" ref="AI71:AI131" si="21">ROUND(G71*U71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ71" s="1"/>
+        <f t="shared" ref="AI71:AI131" si="23">ROUND(G71*U71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AK71" s="1"/>
       <c r="AL71" s="1"/>
       <c r="AM71" s="1"/>
@@ -8794,7 +8984,7 @@
         <v>203.1</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-24.406000000000006</v>
       </c>
       <c r="M72" s="1"/>
@@ -8808,23 +8998,23 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>35.738799999999998</v>
       </c>
       <c r="T72" s="5">
-        <f t="shared" ref="T72:T77" si="22">12*S72-R72-Q72-P72-O72-F72</f>
+        <f t="shared" ref="T72:T77" si="24">12*S72-R72-Q72-P72-O72-F72</f>
         <v>41.889800000000122</v>
       </c>
       <c r="U72" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>41.889800000000122</v>
       </c>
       <c r="V72" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W72" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.827890136210502</v>
       </c>
       <c r="X72" s="1">
@@ -8859,10 +9049,13 @@
       </c>
       <c r="AH72" s="1"/>
       <c r="AI72" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>42</v>
       </c>
-      <c r="AJ72" s="1"/>
+      <c r="AJ72" s="1">
+        <f t="shared" si="13"/>
+        <v>283.01623636363638</v>
+      </c>
       <c r="AK72" s="1"/>
       <c r="AL72" s="1"/>
       <c r="AM72" s="1"/>
@@ -8907,7 +9100,7 @@
         <v>76</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-17</v>
       </c>
       <c r="M73" s="1"/>
@@ -8921,20 +9114,20 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>11.8</v>
       </c>
       <c r="T73" s="5"/>
       <c r="U73" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V73" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>17.110169491525422</v>
       </c>
       <c r="W73" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>17.110169491525422</v>
       </c>
       <c r="X73" s="1">
@@ -8969,10 +9162,13 @@
       </c>
       <c r="AH73" s="1"/>
       <c r="AI73" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ73" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="1">
+        <f t="shared" si="13"/>
+        <v>126.38181818181818</v>
+      </c>
       <c r="AK73" s="1"/>
       <c r="AL73" s="1"/>
       <c r="AM73" s="1"/>
@@ -9017,7 +9213,7 @@
         <v>156</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="M74" s="1"/>
@@ -9031,23 +9227,23 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>32.6</v>
       </c>
       <c r="T74" s="5">
+        <f t="shared" si="24"/>
+        <v>125.31000000000006</v>
+      </c>
+      <c r="U74" s="5">
+        <f t="shared" si="20"/>
+        <v>125.31000000000006</v>
+      </c>
+      <c r="V74" s="1">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="W74" s="1">
         <f t="shared" si="22"/>
-        <v>125.31000000000006</v>
-      </c>
-      <c r="U74" s="5">
-        <f t="shared" si="18"/>
-        <v>125.31000000000006</v>
-      </c>
-      <c r="V74" s="1">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="W74" s="1">
-        <f t="shared" si="20"/>
         <v>8.1561349693251532</v>
       </c>
       <c r="X74" s="1">
@@ -9082,10 +9278,13 @@
       </c>
       <c r="AH74" s="1"/>
       <c r="AI74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>75</v>
       </c>
-      <c r="AJ74" s="1"/>
+      <c r="AJ74" s="1">
+        <f t="shared" si="13"/>
+        <v>226.16363636363639</v>
+      </c>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1"/>
       <c r="AM74" s="1"/>
@@ -9130,7 +9329,7 @@
         <v>120</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-11</v>
       </c>
       <c r="M75" s="1"/>
@@ -9144,23 +9343,23 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>21.8</v>
       </c>
       <c r="T75" s="5">
+        <f t="shared" si="24"/>
+        <v>108.60000000000002</v>
+      </c>
+      <c r="U75" s="5">
+        <f t="shared" si="20"/>
+        <v>108.60000000000002</v>
+      </c>
+      <c r="V75" s="1">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="W75" s="1">
         <f t="shared" si="22"/>
-        <v>108.60000000000002</v>
-      </c>
-      <c r="U75" s="5">
-        <f t="shared" si="18"/>
-        <v>108.60000000000002</v>
-      </c>
-      <c r="V75" s="1">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="W75" s="1">
-        <f t="shared" si="20"/>
         <v>7.0183486238532105</v>
       </c>
       <c r="X75" s="1">
@@ -9195,10 +9394,13 @@
       </c>
       <c r="AH75" s="1"/>
       <c r="AI75" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>43</v>
       </c>
-      <c r="AJ75" s="1"/>
+      <c r="AJ75" s="1">
+        <f t="shared" si="13"/>
+        <v>151.83636363636364</v>
+      </c>
       <c r="AK75" s="1"/>
       <c r="AL75" s="1"/>
       <c r="AM75" s="1"/>
@@ -9243,7 +9445,7 @@
         <v>163</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-20</v>
       </c>
       <c r="M76" s="1"/>
@@ -9257,23 +9459,23 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>28.6</v>
       </c>
       <c r="T76" s="5">
+        <f t="shared" si="24"/>
+        <v>68.000000000000114</v>
+      </c>
+      <c r="U76" s="5">
+        <f t="shared" si="20"/>
+        <v>68.000000000000114</v>
+      </c>
+      <c r="V76" s="1">
+        <f t="shared" si="21"/>
+        <v>12.000000000000002</v>
+      </c>
+      <c r="W76" s="1">
         <f t="shared" si="22"/>
-        <v>68.000000000000114</v>
-      </c>
-      <c r="U76" s="5">
-        <f t="shared" si="18"/>
-        <v>68.000000000000114</v>
-      </c>
-      <c r="V76" s="1">
-        <f t="shared" si="19"/>
-        <v>12.000000000000002</v>
-      </c>
-      <c r="W76" s="1">
-        <f t="shared" si="20"/>
         <v>9.6223776223776198</v>
       </c>
       <c r="X76" s="1">
@@ -9308,10 +9510,13 @@
       </c>
       <c r="AH76" s="1"/>
       <c r="AI76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>22</v>
       </c>
-      <c r="AJ76" s="1"/>
+      <c r="AJ76" s="1">
+        <f t="shared" si="13"/>
+        <v>194.09090909090907</v>
+      </c>
       <c r="AK76" s="1"/>
       <c r="AL76" s="1"/>
       <c r="AM76" s="1"/>
@@ -9356,7 +9561,7 @@
         <v>152</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-1</v>
       </c>
       <c r="M77" s="1"/>
@@ -9370,23 +9575,23 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>30.2</v>
       </c>
       <c r="T77" s="5">
+        <f t="shared" si="24"/>
+        <v>61.999999999999943</v>
+      </c>
+      <c r="U77" s="5">
+        <f t="shared" si="20"/>
+        <v>61.999999999999943</v>
+      </c>
+      <c r="V77" s="1">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="W77" s="1">
         <f t="shared" si="22"/>
-        <v>61.999999999999943</v>
-      </c>
-      <c r="U77" s="5">
-        <f t="shared" si="18"/>
-        <v>61.999999999999943</v>
-      </c>
-      <c r="V77" s="1">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="W77" s="1">
-        <f t="shared" si="20"/>
         <v>9.9470198675496704</v>
       </c>
       <c r="X77" s="1">
@@ -9421,10 +9626,13 @@
       </c>
       <c r="AH77" s="1"/>
       <c r="AI77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>22</v>
       </c>
-      <c r="AJ77" s="1"/>
+      <c r="AJ77" s="1">
+        <f t="shared" si="13"/>
+        <v>195.10909090909092</v>
+      </c>
       <c r="AK77" s="1"/>
       <c r="AL77" s="1"/>
       <c r="AM77" s="1"/>
@@ -9457,7 +9665,7 @@
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
       <c r="L78" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M78" s="10"/>
@@ -9469,20 +9677,20 @@
       <c r="Q78" s="10"/>
       <c r="R78" s="10"/>
       <c r="S78" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T78" s="12"/>
       <c r="U78" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V78" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W78" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X78" s="10">
@@ -9519,10 +9727,13 @@
         <v>44</v>
       </c>
       <c r="AI78" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ78" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AK78" s="1"/>
       <c r="AL78" s="1"/>
       <c r="AM78" s="1"/>
@@ -9567,7 +9778,7 @@
         <v>100</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-13</v>
       </c>
       <c r="M79" s="1"/>
@@ -9581,23 +9792,23 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>17.399999999999999</v>
       </c>
       <c r="T79" s="5">
-        <f t="shared" ref="T79:T81" si="23">12*S79-R79-Q79-P79-O79-F79</f>
+        <f t="shared" ref="T79:T81" si="25">12*S79-R79-Q79-P79-O79-F79</f>
         <v>122.59999999999997</v>
       </c>
       <c r="U79" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>122.59999999999997</v>
       </c>
       <c r="V79" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>11.999999999999998</v>
       </c>
       <c r="W79" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4.9540229885057476</v>
       </c>
       <c r="X79" s="1">
@@ -9632,10 +9843,13 @@
       </c>
       <c r="AH79" s="1"/>
       <c r="AI79" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>74</v>
       </c>
-      <c r="AJ79" s="1"/>
+      <c r="AJ79" s="1">
+        <f t="shared" si="13"/>
+        <v>84</v>
+      </c>
       <c r="AK79" s="1"/>
       <c r="AL79" s="1"/>
       <c r="AM79" s="1"/>
@@ -9680,7 +9894,7 @@
         <v>46</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-19</v>
       </c>
       <c r="M80" s="1"/>
@@ -9694,20 +9908,20 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5.4</v>
       </c>
       <c r="T80" s="5"/>
       <c r="U80" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V80" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>30.185185185185183</v>
       </c>
       <c r="W80" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>30.185185185185183</v>
       </c>
       <c r="X80" s="1">
@@ -9742,10 +9956,13 @@
       </c>
       <c r="AH80" s="1"/>
       <c r="AI80" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ80" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="1">
+        <f t="shared" si="13"/>
+        <v>59.309090909090898</v>
+      </c>
       <c r="AK80" s="1"/>
       <c r="AL80" s="1"/>
       <c r="AM80" s="1"/>
@@ -9790,7 +10007,7 @@
         <v>63</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-11</v>
       </c>
       <c r="M81" s="1"/>
@@ -9804,23 +10021,23 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>10.4</v>
       </c>
       <c r="T81" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7.9560000000000208</v>
       </c>
       <c r="U81" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>7.9560000000000208</v>
       </c>
       <c r="V81" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W81" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>11.234999999999999</v>
       </c>
       <c r="X81" s="1">
@@ -9855,10 +10072,13 @@
       </c>
       <c r="AH81" s="1"/>
       <c r="AI81" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
-      <c r="AJ81" s="1"/>
+      <c r="AJ81" s="1">
+        <f t="shared" si="13"/>
+        <v>51.036363636363639</v>
+      </c>
       <c r="AK81" s="1"/>
       <c r="AL81" s="1"/>
       <c r="AM81" s="1"/>
@@ -9903,7 +10123,7 @@
         <v>25</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-3</v>
       </c>
       <c r="M82" s="1"/>
@@ -9917,22 +10137,22 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="T82" s="5">
         <v>8</v>
       </c>
       <c r="U82" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>8</v>
       </c>
       <c r="V82" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12.727272727272727</v>
       </c>
       <c r="W82" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.909090909090908</v>
       </c>
       <c r="X82" s="1">
@@ -9967,10 +10187,13 @@
       </c>
       <c r="AH82" s="1"/>
       <c r="AI82" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
-      <c r="AJ82" s="1"/>
+      <c r="AJ82" s="1">
+        <f t="shared" si="13"/>
+        <v>42</v>
+      </c>
       <c r="AK82" s="1"/>
       <c r="AL82" s="1"/>
       <c r="AM82" s="1"/>
@@ -10015,7 +10238,7 @@
         <v>177</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>6</v>
       </c>
       <c r="M83" s="1"/>
@@ -10031,7 +10254,7 @@
       </c>
       <c r="R83" s="1"/>
       <c r="S83" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>36.6</v>
       </c>
       <c r="T83" s="5">
@@ -10039,15 +10262,15 @@
         <v>234.20000000000005</v>
       </c>
       <c r="U83" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>234.20000000000005</v>
       </c>
       <c r="V83" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>11</v>
       </c>
       <c r="W83" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4.6010928961748627</v>
       </c>
       <c r="X83" s="1">
@@ -10082,10 +10305,13 @@
       </c>
       <c r="AH83" s="1"/>
       <c r="AI83" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>82</v>
       </c>
-      <c r="AJ83" s="1"/>
+      <c r="AJ83" s="1">
+        <f t="shared" si="13"/>
+        <v>200.32727272727269</v>
+      </c>
       <c r="AK83" s="1"/>
       <c r="AL83" s="1"/>
       <c r="AM83" s="1"/>
@@ -10118,7 +10344,7 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M84" s="10"/>
@@ -10130,20 +10356,20 @@
       <c r="Q84" s="10"/>
       <c r="R84" s="10"/>
       <c r="S84" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T84" s="12"/>
       <c r="U84" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V84" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W84" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X84" s="10">
@@ -10180,10 +10406,13 @@
         <v>44</v>
       </c>
       <c r="AI84" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ84" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AK84" s="1"/>
       <c r="AL84" s="1"/>
       <c r="AM84" s="1"/>
@@ -10216,7 +10445,7 @@
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M85" s="10"/>
@@ -10228,20 +10457,20 @@
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
       <c r="S85" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T85" s="12"/>
       <c r="U85" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V85" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W85" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X85" s="10">
@@ -10278,10 +10507,13 @@
         <v>44</v>
       </c>
       <c r="AI85" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ85" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AK85" s="1"/>
       <c r="AL85" s="1"/>
       <c r="AM85" s="1"/>
@@ -10314,7 +10546,7 @@
       <c r="J86" s="10"/>
       <c r="K86" s="10"/>
       <c r="L86" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M86" s="10"/>
@@ -10326,20 +10558,20 @@
       <c r="Q86" s="10"/>
       <c r="R86" s="10"/>
       <c r="S86" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T86" s="12"/>
       <c r="U86" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V86" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W86" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X86" s="10">
@@ -10376,10 +10608,13 @@
         <v>44</v>
       </c>
       <c r="AI86" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ86" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AK86" s="1"/>
       <c r="AL86" s="1"/>
       <c r="AM86" s="1"/>
@@ -10424,7 +10659,7 @@
         <v>221.3</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-2.2630000000000052</v>
       </c>
       <c r="M87" s="1"/>
@@ -10438,7 +10673,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>43.807400000000001</v>
       </c>
       <c r="T87" s="5">
@@ -10450,11 +10685,11 @@
         <v>126.48334800000003</v>
       </c>
       <c r="V87" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>14.02</v>
       </c>
       <c r="W87" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>11.132740130662855</v>
       </c>
       <c r="X87" s="1">
@@ -10489,10 +10724,13 @@
       </c>
       <c r="AH87" s="1"/>
       <c r="AI87" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>126</v>
       </c>
-      <c r="AJ87" s="1"/>
+      <c r="AJ87" s="1">
+        <f t="shared" si="13"/>
+        <v>295.47674545454538</v>
+      </c>
       <c r="AK87" s="1"/>
       <c r="AL87" s="1"/>
       <c r="AM87" s="1"/>
@@ -10525,7 +10763,7 @@
       <c r="J88" s="10"/>
       <c r="K88" s="10"/>
       <c r="L88" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M88" s="10"/>
@@ -10537,20 +10775,20 @@
       <c r="Q88" s="10"/>
       <c r="R88" s="10"/>
       <c r="S88" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T88" s="12"/>
       <c r="U88" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V88" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W88" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X88" s="10">
@@ -10587,10 +10825,13 @@
         <v>44</v>
       </c>
       <c r="AI88" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ88" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AK88" s="1"/>
       <c r="AL88" s="1"/>
       <c r="AM88" s="1"/>
@@ -10635,7 +10876,7 @@
         <v>1684.9939999999999</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-21.631999999999834</v>
       </c>
       <c r="M89" s="1"/>
@@ -10651,23 +10892,23 @@
         <v>800</v>
       </c>
       <c r="S89" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>332.67240000000004</v>
       </c>
       <c r="T89" s="5">
-        <f t="shared" ref="T89:T91" si="24">12*S89-R89-Q89-P89-O89-F89</f>
+        <f t="shared" ref="T89:T91" si="26">12*S89-R89-Q89-P89-O89-F89</f>
         <v>407.12527000000046</v>
       </c>
       <c r="U89" s="5">
-        <f t="shared" ref="U89:U91" si="25">T89+$U$1*S89</f>
+        <f t="shared" ref="U89:U91" si="27">T89+$U$1*S89</f>
         <v>1079.1235180000006</v>
       </c>
       <c r="V89" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>14.020000000000001</v>
       </c>
       <c r="W89" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.776197634670023</v>
       </c>
       <c r="X89" s="1">
@@ -10702,10 +10943,13 @@
       </c>
       <c r="AH89" s="1"/>
       <c r="AI89" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1079</v>
       </c>
-      <c r="AJ89" s="1"/>
+      <c r="AJ89" s="1">
+        <f t="shared" si="13"/>
+        <v>2167.3663454545454</v>
+      </c>
       <c r="AK89" s="1"/>
       <c r="AL89" s="1"/>
       <c r="AM89" s="1"/>
@@ -10750,7 +10994,7 @@
         <v>1251.5</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>2.5389999999999873</v>
       </c>
       <c r="M90" s="1"/>
@@ -10766,23 +11010,23 @@
         <v>600</v>
       </c>
       <c r="S90" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>250.80779999999999</v>
       </c>
       <c r="T90" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>431.38566999999989</v>
       </c>
       <c r="U90" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>938.01742599999989</v>
       </c>
       <c r="V90" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>14.02</v>
       </c>
       <c r="W90" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.280014935739638</v>
       </c>
       <c r="X90" s="1">
@@ -10817,10 +11061,13 @@
       </c>
       <c r="AH90" s="1"/>
       <c r="AI90" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>938</v>
       </c>
-      <c r="AJ90" s="1"/>
+      <c r="AJ90" s="1">
+        <f t="shared" si="13"/>
+        <v>1668.2928181818181</v>
+      </c>
       <c r="AK90" s="1"/>
       <c r="AL90" s="1"/>
       <c r="AM90" s="1"/>
@@ -10865,7 +11112,7 @@
         <v>2150.5</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-79.494000000000142</v>
       </c>
       <c r="M91" s="1"/>
@@ -10879,23 +11126,23 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>414.20119999999997</v>
       </c>
       <c r="T91" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>977.4931500000007</v>
       </c>
       <c r="U91" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1814.1795740000007</v>
       </c>
       <c r="V91" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>14.020000000000001</v>
       </c>
       <c r="W91" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>9.640052346540763</v>
       </c>
       <c r="X91" s="1">
@@ -10930,10 +11177,13 @@
       </c>
       <c r="AH91" s="1"/>
       <c r="AI91" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1814</v>
       </c>
-      <c r="AJ91" s="1"/>
+      <c r="AJ91" s="1">
+        <f t="shared" si="13"/>
+        <v>2923.1776</v>
+      </c>
       <c r="AK91" s="1"/>
       <c r="AL91" s="1"/>
       <c r="AM91" s="1"/>
@@ -10966,7 +11216,7 @@
       <c r="J92" s="10"/>
       <c r="K92" s="10"/>
       <c r="L92" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M92" s="10"/>
@@ -10978,20 +11228,20 @@
       <c r="Q92" s="10"/>
       <c r="R92" s="10"/>
       <c r="S92" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T92" s="12"/>
       <c r="U92" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V92" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W92" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X92" s="10">
@@ -11028,10 +11278,13 @@
         <v>44</v>
       </c>
       <c r="AI92" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ92" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="1">
+        <f t="shared" ref="AJ92:AJ131" si="28">(S92+X92+Y92+Z92+AA92+AB92+AC92+AD92+AE92+AF92+AG92)/11*7</f>
+        <v>0</v>
+      </c>
       <c r="AK92" s="1"/>
       <c r="AL92" s="1"/>
       <c r="AM92" s="1"/>
@@ -11076,7 +11329,7 @@
         <v>146</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-18</v>
       </c>
       <c r="M93" s="1"/>
@@ -11090,7 +11343,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>25.6</v>
       </c>
       <c r="T93" s="5">
@@ -11098,15 +11351,15 @@
         <v>142.20000000000005</v>
       </c>
       <c r="U93" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>142.20000000000005</v>
       </c>
       <c r="V93" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12.000000000000002</v>
       </c>
       <c r="W93" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>6.4453125</v>
       </c>
       <c r="X93" s="1">
@@ -11141,10 +11394,13 @@
       </c>
       <c r="AH93" s="1"/>
       <c r="AI93" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>43</v>
       </c>
-      <c r="AJ93" s="1"/>
+      <c r="AJ93" s="1">
+        <f t="shared" si="28"/>
+        <v>140.76363636363635</v>
+      </c>
       <c r="AK93" s="1"/>
       <c r="AL93" s="1"/>
       <c r="AM93" s="1"/>
@@ -11177,7 +11433,7 @@
       <c r="J94" s="10"/>
       <c r="K94" s="10"/>
       <c r="L94" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M94" s="10"/>
@@ -11189,20 +11445,20 @@
       <c r="Q94" s="10"/>
       <c r="R94" s="10"/>
       <c r="S94" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T94" s="12"/>
       <c r="U94" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V94" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W94" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X94" s="10">
@@ -11239,10 +11495,13 @@
         <v>44</v>
       </c>
       <c r="AI94" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ94" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AK94" s="1"/>
       <c r="AL94" s="1"/>
       <c r="AM94" s="1"/>
@@ -11287,7 +11546,7 @@
         <v>74</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-9</v>
       </c>
       <c r="M95" s="1"/>
@@ -11301,23 +11560,23 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>13</v>
       </c>
       <c r="T95" s="5">
-        <f t="shared" ref="T95:T97" si="26">12*S95-R95-Q95-P95-O95-F95</f>
+        <f t="shared" ref="T95:T97" si="29">12*S95-R95-Q95-P95-O95-F95</f>
         <v>45.399999999999977</v>
       </c>
       <c r="U95" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>45.399999999999977</v>
       </c>
       <c r="V95" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W95" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>8.5076923076923094</v>
       </c>
       <c r="X95" s="1">
@@ -11352,10 +11611,13 @@
       </c>
       <c r="AH95" s="1"/>
       <c r="AI95" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
-      <c r="AJ95" s="1"/>
+      <c r="AJ95" s="1">
+        <f t="shared" si="28"/>
+        <v>90.61818181818181</v>
+      </c>
       <c r="AK95" s="1"/>
       <c r="AL95" s="1"/>
       <c r="AM95" s="1"/>
@@ -11400,7 +11662,7 @@
         <v>101</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-26</v>
       </c>
       <c r="M96" s="1"/>
@@ -11414,23 +11676,23 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>15</v>
       </c>
       <c r="T96" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>15.399999999999977</v>
       </c>
       <c r="U96" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>15.399999999999977</v>
       </c>
       <c r="V96" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W96" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.973333333333334</v>
       </c>
       <c r="X96" s="1">
@@ -11465,10 +11727,13 @@
       </c>
       <c r="AH96" s="1"/>
       <c r="AI96" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="AJ96" s="1"/>
+      <c r="AJ96" s="1">
+        <f t="shared" si="28"/>
+        <v>98.63636363636364</v>
+      </c>
       <c r="AK96" s="1"/>
       <c r="AL96" s="1"/>
       <c r="AM96" s="1"/>
@@ -11513,7 +11778,7 @@
         <v>59</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-8</v>
       </c>
       <c r="M97" s="1"/>
@@ -11527,23 +11792,23 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
       <c r="S97" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>10.199999999999999</v>
       </c>
       <c r="T97" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>13.59999999999998</v>
       </c>
       <c r="U97" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>13.59999999999998</v>
       </c>
       <c r="V97" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W97" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.666666666666668</v>
       </c>
       <c r="X97" s="1">
@@ -11578,10 +11843,13 @@
       </c>
       <c r="AH97" s="1"/>
       <c r="AI97" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="AJ97" s="1"/>
+      <c r="AJ97" s="1">
+        <f t="shared" si="28"/>
+        <v>65.036363636363632</v>
+      </c>
       <c r="AK97" s="1"/>
       <c r="AL97" s="1"/>
       <c r="AM97" s="1"/>
@@ -11626,7 +11894,7 @@
         <v>92</v>
       </c>
       <c r="L98" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-20</v>
       </c>
       <c r="M98" s="10"/>
@@ -11640,20 +11908,20 @@
       <c r="Q98" s="10"/>
       <c r="R98" s="10"/>
       <c r="S98" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>14.4</v>
       </c>
       <c r="T98" s="12"/>
       <c r="U98" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V98" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>13.236111111111111</v>
       </c>
       <c r="W98" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>13.236111111111111</v>
       </c>
       <c r="X98" s="10">
@@ -11688,10 +11956,13 @@
       </c>
       <c r="AH98" s="10"/>
       <c r="AI98" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ98" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="1">
+        <f t="shared" si="28"/>
+        <v>94.309090909090898</v>
+      </c>
       <c r="AK98" s="1"/>
       <c r="AL98" s="1"/>
       <c r="AM98" s="1"/>
@@ -11732,7 +12003,7 @@
         <v>24</v>
       </c>
       <c r="L99" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-17</v>
       </c>
       <c r="M99" s="10"/>
@@ -11746,20 +12017,20 @@
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
       <c r="S99" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1.4</v>
       </c>
       <c r="T99" s="12"/>
       <c r="U99" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V99" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W99" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="X99" s="10">
@@ -11796,10 +12067,13 @@
         <v>141</v>
       </c>
       <c r="AI99" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ99" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="1">
+        <f t="shared" si="28"/>
+        <v>64.272727272727266</v>
+      </c>
       <c r="AK99" s="1"/>
       <c r="AL99" s="1"/>
       <c r="AM99" s="1"/>
@@ -11832,7 +12106,7 @@
       <c r="J100" s="10"/>
       <c r="K100" s="10"/>
       <c r="L100" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M100" s="10"/>
@@ -11844,20 +12118,20 @@
       <c r="Q100" s="10"/>
       <c r="R100" s="10"/>
       <c r="S100" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T100" s="12"/>
       <c r="U100" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V100" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W100" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X100" s="10">
@@ -11894,10 +12168,13 @@
         <v>44</v>
       </c>
       <c r="AI100" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ100" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AK100" s="1"/>
       <c r="AL100" s="1"/>
       <c r="AM100" s="1"/>
@@ -11942,7 +12219,7 @@
         <v>7.9</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3.0860000000000003</v>
       </c>
       <c r="M101" s="1"/>
@@ -11956,20 +12233,20 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
       <c r="S101" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2.1972</v>
       </c>
       <c r="T101" s="5"/>
       <c r="U101" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V101" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>40.201165119242674</v>
       </c>
       <c r="W101" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>40.201165119242674</v>
       </c>
       <c r="X101" s="1">
@@ -12002,14 +12279,17 @@
       <c r="AG101" s="1">
         <v>1.6108</v>
       </c>
-      <c r="AH101" s="14" t="s">
+      <c r="AH101" s="13" t="s">
         <v>67</v>
       </c>
       <c r="AI101" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ101" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="1">
+        <f t="shared" si="28"/>
+        <v>135.54519999999999</v>
+      </c>
       <c r="AK101" s="1"/>
       <c r="AL101" s="1"/>
       <c r="AM101" s="1"/>
@@ -12048,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L131" si="27">E102-K102</f>
+        <f t="shared" ref="L102:L131" si="30">E102-K102</f>
         <v>-1</v>
       </c>
       <c r="M102" s="1"/>
@@ -12062,20 +12342,20 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
       <c r="S102" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T102" s="5"/>
       <c r="U102" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V102" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W102" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X102" s="1">
@@ -12110,10 +12390,13 @@
       </c>
       <c r="AH102" s="1"/>
       <c r="AI102" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ102" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="1">
+        <f t="shared" si="28"/>
+        <v>-1.1454545454545453</v>
+      </c>
       <c r="AK102" s="1"/>
       <c r="AL102" s="1"/>
       <c r="AM102" s="1"/>
@@ -12146,7 +12429,7 @@
       <c r="J103" s="10"/>
       <c r="K103" s="10"/>
       <c r="L103" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M103" s="10"/>
@@ -12158,20 +12441,20 @@
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
       <c r="S103" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T103" s="12"/>
       <c r="U103" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V103" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W103" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X103" s="10">
@@ -12208,10 +12491,13 @@
         <v>44</v>
       </c>
       <c r="AI103" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ103" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ103" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AK103" s="1"/>
       <c r="AL103" s="1"/>
       <c r="AM103" s="1"/>
@@ -12256,7 +12542,7 @@
         <v>97</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-20</v>
       </c>
       <c r="M104" s="1"/>
@@ -12270,23 +12556,23 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
       <c r="S104" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>15.4</v>
       </c>
       <c r="T104" s="5">
-        <f t="shared" ref="T104:T108" si="28">12*S104-R104-Q104-P104-O104-F104</f>
+        <f t="shared" ref="T104:T108" si="31">12*S104-R104-Q104-P104-O104-F104</f>
         <v>17.800000000000011</v>
       </c>
       <c r="U104" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>17.800000000000011</v>
       </c>
       <c r="V104" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W104" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.844155844155845</v>
       </c>
       <c r="X104" s="1">
@@ -12321,10 +12607,13 @@
       </c>
       <c r="AH104" s="1"/>
       <c r="AI104" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="AJ104" s="1"/>
+      <c r="AJ104" s="1">
+        <f t="shared" si="28"/>
+        <v>128.67272727272729</v>
+      </c>
       <c r="AK104" s="1"/>
       <c r="AL104" s="1"/>
       <c r="AM104" s="1"/>
@@ -12369,7 +12658,7 @@
         <v>76</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-14</v>
       </c>
       <c r="M105" s="1"/>
@@ -12383,22 +12672,22 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
       <c r="S105" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>12.4</v>
       </c>
       <c r="T105" s="5">
         <v>20</v>
       </c>
       <c r="U105" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="V105" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>13.520322580645161</v>
       </c>
       <c r="W105" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>11.907419354838709</v>
       </c>
       <c r="X105" s="1">
@@ -12433,10 +12722,13 @@
       </c>
       <c r="AH105" s="1"/>
       <c r="AI105" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
-      <c r="AJ105" s="1"/>
+      <c r="AJ105" s="1">
+        <f t="shared" si="28"/>
+        <v>110.47272727272727</v>
+      </c>
       <c r="AK105" s="1"/>
       <c r="AL105" s="1"/>
       <c r="AM105" s="1"/>
@@ -12481,7 +12773,7 @@
         <v>3</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-1</v>
       </c>
       <c r="M106" s="1"/>
@@ -12495,20 +12787,20 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
       <c r="S106" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.4</v>
       </c>
       <c r="T106" s="5"/>
       <c r="U106" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V106" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>45</v>
       </c>
       <c r="W106" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>45</v>
       </c>
       <c r="X106" s="1">
@@ -12543,10 +12835,13 @@
       </c>
       <c r="AH106" s="1"/>
       <c r="AI106" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ106" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ106" s="1">
+        <f t="shared" si="28"/>
+        <v>0.12727272727272732</v>
+      </c>
       <c r="AK106" s="1"/>
       <c r="AL106" s="1"/>
       <c r="AM106" s="1"/>
@@ -12591,7 +12886,7 @@
         <v>166.57</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-9.6059999999999945</v>
       </c>
       <c r="M107" s="1"/>
@@ -12605,23 +12900,23 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
       <c r="S107" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>31.392800000000001</v>
       </c>
       <c r="T107" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>165.37879999999998</v>
       </c>
       <c r="U107" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>165.37879999999998</v>
       </c>
       <c r="V107" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12.000000000000002</v>
       </c>
       <c r="W107" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>6.7319512754516975</v>
       </c>
       <c r="X107" s="1">
@@ -12656,10 +12951,13 @@
       </c>
       <c r="AH107" s="1"/>
       <c r="AI107" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>165</v>
       </c>
-      <c r="AJ107" s="1"/>
+      <c r="AJ107" s="1">
+        <f t="shared" si="28"/>
+        <v>219.02465454545455</v>
+      </c>
       <c r="AK107" s="1"/>
       <c r="AL107" s="1"/>
       <c r="AM107" s="1"/>
@@ -12704,7 +13002,7 @@
         <v>121.1</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>10.093000000000018</v>
       </c>
       <c r="M108" s="1"/>
@@ -12718,23 +13016,23 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
       <c r="S108" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>26.238600000000002</v>
       </c>
       <c r="T108" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>108.71920000000001</v>
       </c>
       <c r="U108" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>108.71920000000001</v>
       </c>
       <c r="V108" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12.000000000000002</v>
       </c>
       <c r="W108" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>7.856516734886771</v>
       </c>
       <c r="X108" s="1">
@@ -12769,10 +13067,13 @@
       </c>
       <c r="AH108" s="1"/>
       <c r="AI108" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>109</v>
       </c>
-      <c r="AJ108" s="1"/>
+      <c r="AJ108" s="1">
+        <f t="shared" si="28"/>
+        <v>153.54499999999999</v>
+      </c>
       <c r="AK108" s="1"/>
       <c r="AL108" s="1"/>
       <c r="AM108" s="1"/>
@@ -12817,7 +13118,7 @@
         <v>39.5</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-22.213000000000001</v>
       </c>
       <c r="M109" s="1"/>
@@ -12831,20 +13132,20 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
       <c r="S109" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3.4573999999999998</v>
       </c>
       <c r="T109" s="5"/>
       <c r="U109" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V109" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>92.7067651992827</v>
       </c>
       <c r="W109" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>92.7067651992827</v>
       </c>
       <c r="X109" s="1">
@@ -12879,10 +13180,13 @@
       </c>
       <c r="AH109" s="1"/>
       <c r="AI109" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ109" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="1">
+        <f t="shared" si="28"/>
+        <v>75.993272727272711</v>
+      </c>
       <c r="AK109" s="1"/>
       <c r="AL109" s="1"/>
       <c r="AM109" s="1"/>
@@ -12915,7 +13219,7 @@
       <c r="J110" s="10"/>
       <c r="K110" s="10"/>
       <c r="L110" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M110" s="10"/>
@@ -12927,20 +13231,20 @@
       <c r="Q110" s="10"/>
       <c r="R110" s="10"/>
       <c r="S110" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T110" s="12"/>
       <c r="U110" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V110" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W110" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X110" s="10">
@@ -12977,10 +13281,13 @@
         <v>44</v>
       </c>
       <c r="AI110" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ110" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ110" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AK110" s="1"/>
       <c r="AL110" s="1"/>
       <c r="AM110" s="1"/>
@@ -13013,7 +13320,7 @@
       <c r="J111" s="10"/>
       <c r="K111" s="10"/>
       <c r="L111" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M111" s="10"/>
@@ -13025,20 +13332,20 @@
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
       <c r="S111" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T111" s="12"/>
       <c r="U111" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V111" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W111" s="10" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X111" s="10">
@@ -13075,10 +13382,13 @@
         <v>44</v>
       </c>
       <c r="AI111" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ111" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="1">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AK111" s="1"/>
       <c r="AL111" s="1"/>
       <c r="AM111" s="1"/>
@@ -13123,7 +13433,7 @@
         <v>346</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-82</v>
       </c>
       <c r="M112" s="1"/>
@@ -13137,23 +13447,23 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
       <c r="S112" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>52.8</v>
       </c>
       <c r="T112" s="5">
-        <f t="shared" ref="T112:T127" si="29">12*S112-R112-Q112-P112-O112-F112</f>
+        <f t="shared" ref="T112:T127" si="32">12*S112-R112-Q112-P112-O112-F112</f>
         <v>133.39999999999992</v>
       </c>
       <c r="U112" s="5">
-        <f t="shared" ref="U112:U114" si="30">T112+$U$1*S112</f>
+        <f t="shared" ref="U112:U114" si="33">T112+$U$1*S112</f>
         <v>240.05599999999993</v>
       </c>
       <c r="V112" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>14.019999999999998</v>
       </c>
       <c r="W112" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>9.4734848484848495</v>
       </c>
       <c r="X112" s="1">
@@ -13188,10 +13498,13 @@
       </c>
       <c r="AH112" s="1"/>
       <c r="AI112" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>67</v>
       </c>
-      <c r="AJ112" s="1"/>
+      <c r="AJ112" s="1">
+        <f t="shared" si="28"/>
+        <v>327.09090909090907</v>
+      </c>
       <c r="AK112" s="1"/>
       <c r="AL112" s="1"/>
       <c r="AM112" s="1"/>
@@ -13236,7 +13549,7 @@
         <v>296</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-63</v>
       </c>
       <c r="M113" s="1"/>
@@ -13250,7 +13563,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
       <c r="S113" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>46.6</v>
       </c>
       <c r="T113" s="5">
@@ -13258,15 +13571,15 @@
         <v>317</v>
       </c>
       <c r="U113" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>411.13200000000001</v>
       </c>
       <c r="V113" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12.020000000000001</v>
       </c>
       <c r="W113" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>3.1974248927038627</v>
       </c>
       <c r="X113" s="1">
@@ -13301,10 +13614,13 @@
       </c>
       <c r="AH113" s="1"/>
       <c r="AI113" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>115</v>
       </c>
-      <c r="AJ113" s="1"/>
+      <c r="AJ113" s="1">
+        <f t="shared" si="28"/>
+        <v>106.01818181818182</v>
+      </c>
       <c r="AK113" s="1"/>
       <c r="AL113" s="1"/>
       <c r="AM113" s="1"/>
@@ -13349,7 +13665,7 @@
         <v>332</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-107</v>
       </c>
       <c r="M114" s="1"/>
@@ -13363,23 +13679,23 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
       <c r="S114" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>45</v>
       </c>
       <c r="T114" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>164</v>
       </c>
       <c r="U114" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>254.9</v>
       </c>
       <c r="V114" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>14.02</v>
       </c>
       <c r="W114" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>8.3555555555555561</v>
       </c>
       <c r="X114" s="1">
@@ -13414,10 +13730,13 @@
       </c>
       <c r="AH114" s="1"/>
       <c r="AI114" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>71</v>
       </c>
-      <c r="AJ114" s="1"/>
+      <c r="AJ114" s="1">
+        <f t="shared" si="28"/>
+        <v>293.61818181818182</v>
+      </c>
       <c r="AK114" s="1"/>
       <c r="AL114" s="1"/>
       <c r="AM114" s="1"/>
@@ -13462,7 +13781,7 @@
         <v>40</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-7</v>
       </c>
       <c r="M115" s="1"/>
@@ -13476,23 +13795,23 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
       <c r="S115" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>6.6</v>
       </c>
       <c r="T115" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>38.199999999999989</v>
       </c>
       <c r="U115" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>38.199999999999989</v>
       </c>
       <c r="V115" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>11.999999999999998</v>
       </c>
       <c r="W115" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>6.2121212121212128</v>
       </c>
       <c r="X115" s="1">
@@ -13529,10 +13848,13 @@
         <v>158</v>
       </c>
       <c r="AI115" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>3</v>
       </c>
-      <c r="AJ115" s="1"/>
+      <c r="AJ115" s="1">
+        <f t="shared" si="28"/>
+        <v>22.527272727272727</v>
+      </c>
       <c r="AK115" s="1"/>
       <c r="AL115" s="1"/>
       <c r="AM115" s="1"/>
@@ -13577,7 +13899,7 @@
         <v>105</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-10.135000000000005</v>
       </c>
       <c r="M116" s="1"/>
@@ -13591,23 +13913,23 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
       <c r="S116" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>18.972999999999999</v>
       </c>
       <c r="T116" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>26.090399999999995</v>
       </c>
       <c r="U116" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>26.090399999999995</v>
       </c>
       <c r="V116" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W116" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>10.624866916143995</v>
       </c>
       <c r="X116" s="1">
@@ -13642,10 +13964,13 @@
       </c>
       <c r="AH116" s="1"/>
       <c r="AI116" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>26</v>
       </c>
-      <c r="AJ116" s="1"/>
+      <c r="AJ116" s="1">
+        <f t="shared" si="28"/>
+        <v>89.361490909090904</v>
+      </c>
       <c r="AK116" s="1"/>
       <c r="AL116" s="1"/>
       <c r="AM116" s="1"/>
@@ -13690,7 +14015,7 @@
         <v>97.5</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>8.1149999999999949</v>
       </c>
       <c r="M117" s="1"/>
@@ -13704,20 +14029,20 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
       <c r="S117" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>21.122999999999998</v>
       </c>
       <c r="T117" s="5"/>
       <c r="U117" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V117" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>11.951749278038161</v>
       </c>
       <c r="W117" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>11.951749278038161</v>
       </c>
       <c r="X117" s="1">
@@ -13752,10 +14077,13 @@
       </c>
       <c r="AH117" s="1"/>
       <c r="AI117" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ117" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ117" s="1">
+        <f t="shared" si="28"/>
+        <v>136.35719999999995</v>
+      </c>
       <c r="AK117" s="1"/>
       <c r="AL117" s="1"/>
       <c r="AM117" s="1"/>
@@ -13800,7 +14128,7 @@
         <v>42</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-23</v>
       </c>
       <c r="M118" s="1"/>
@@ -13814,20 +14142,20 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
       <c r="S118" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3.8</v>
       </c>
       <c r="T118" s="5"/>
       <c r="U118" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V118" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>19.526315789473685</v>
       </c>
       <c r="W118" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>19.526315789473685</v>
       </c>
       <c r="X118" s="1">
@@ -13862,10 +14190,13 @@
       </c>
       <c r="AH118" s="1"/>
       <c r="AI118" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ118" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ118" s="1">
+        <f t="shared" si="28"/>
+        <v>20.745454545454542</v>
+      </c>
       <c r="AK118" s="1"/>
       <c r="AL118" s="1"/>
       <c r="AM118" s="1"/>
@@ -13910,7 +14241,7 @@
         <v>33</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-17</v>
       </c>
       <c r="M119" s="1"/>
@@ -13924,20 +14255,20 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
       <c r="S119" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3.2</v>
       </c>
       <c r="T119" s="5"/>
       <c r="U119" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V119" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>25.093749999999996</v>
       </c>
       <c r="W119" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>25.093749999999996</v>
       </c>
       <c r="X119" s="1">
@@ -13972,10 +14303,13 @@
       </c>
       <c r="AH119" s="1"/>
       <c r="AI119" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ119" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ119" s="1">
+        <f t="shared" si="28"/>
+        <v>19.599999999999998</v>
+      </c>
       <c r="AK119" s="1"/>
       <c r="AL119" s="1"/>
       <c r="AM119" s="1"/>
@@ -14020,7 +14354,7 @@
         <v>87.566999999999993</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>3.1770000000000067</v>
       </c>
       <c r="M120" s="1"/>
@@ -14034,23 +14368,23 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
       <c r="S120" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>18.148800000000001</v>
       </c>
       <c r="T120" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>109.22620000000002</v>
       </c>
       <c r="U120" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>109.22620000000002</v>
       </c>
       <c r="V120" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W120" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>5.9816296394251953</v>
       </c>
       <c r="X120" s="1">
@@ -14085,10 +14419,13 @@
       </c>
       <c r="AH120" s="1"/>
       <c r="AI120" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>109</v>
       </c>
-      <c r="AJ120" s="1"/>
+      <c r="AJ120" s="1">
+        <f t="shared" si="28"/>
+        <v>103.33603636363637</v>
+      </c>
       <c r="AK120" s="1"/>
       <c r="AL120" s="1"/>
       <c r="AM120" s="1"/>
@@ -14133,7 +14470,7 @@
         <v>166</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-3.5629999999999882</v>
       </c>
       <c r="M121" s="1"/>
@@ -14147,23 +14484,23 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
       <c r="S121" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>32.487400000000001</v>
       </c>
       <c r="T121" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>102.01319999999987</v>
       </c>
       <c r="U121" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>102.01319999999987</v>
       </c>
       <c r="V121" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W121" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>8.8599149208616303</v>
       </c>
       <c r="X121" s="1">
@@ -14198,10 +14535,13 @@
       </c>
       <c r="AH121" s="1"/>
       <c r="AI121" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>102</v>
       </c>
-      <c r="AJ121" s="1"/>
+      <c r="AJ121" s="1">
+        <f t="shared" si="28"/>
+        <v>201.87592727272724</v>
+      </c>
       <c r="AK121" s="1"/>
       <c r="AL121" s="1"/>
       <c r="AM121" s="1"/>
@@ -14246,7 +14586,7 @@
         <v>28.6</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1.8559999999999981</v>
       </c>
       <c r="M122" s="1"/>
@@ -14260,20 +14600,20 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
       <c r="S122" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>6.0911999999999997</v>
       </c>
       <c r="T122" s="5"/>
       <c r="U122" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V122" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>15.229839768846864</v>
       </c>
       <c r="W122" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>15.229839768846864</v>
       </c>
       <c r="X122" s="1">
@@ -14308,10 +14648,13 @@
       </c>
       <c r="AH122" s="1"/>
       <c r="AI122" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ122" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ122" s="1">
+        <f t="shared" si="28"/>
+        <v>38.199254545454551</v>
+      </c>
       <c r="AK122" s="1"/>
       <c r="AL122" s="1"/>
       <c r="AM122" s="1"/>
@@ -14356,7 +14699,7 @@
         <v>1282.5</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-439.93299999999999</v>
       </c>
       <c r="M123" s="1"/>
@@ -14372,20 +14715,20 @@
         <v>600</v>
       </c>
       <c r="S123" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>168.51339999999999</v>
       </c>
       <c r="T123" s="5"/>
       <c r="U123" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V123" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>16.353451951002118</v>
       </c>
       <c r="W123" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>16.353451951002118</v>
       </c>
       <c r="X123" s="1">
@@ -14422,10 +14765,13 @@
         <v>166</v>
       </c>
       <c r="AI123" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ123" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ123" s="1">
+        <f t="shared" si="28"/>
+        <v>848.63023636363653</v>
+      </c>
       <c r="AK123" s="1"/>
       <c r="AL123" s="1"/>
       <c r="AM123" s="1"/>
@@ -14470,7 +14816,7 @@
         <v>159</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-62</v>
       </c>
       <c r="M124" s="1"/>
@@ -14484,20 +14830,20 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
       <c r="S124" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>19.399999999999999</v>
       </c>
       <c r="T124" s="5"/>
       <c r="U124" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V124" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>22.704123711340205</v>
       </c>
       <c r="W124" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>22.704123711340205</v>
       </c>
       <c r="X124" s="1">
@@ -14532,10 +14878,13 @@
       </c>
       <c r="AH124" s="1"/>
       <c r="AI124" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ124" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ124" s="1">
+        <f t="shared" si="28"/>
+        <v>251.3636363636364</v>
+      </c>
       <c r="AK124" s="1"/>
       <c r="AL124" s="1"/>
       <c r="AM124" s="1"/>
@@ -14580,7 +14929,7 @@
         <v>89</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-52</v>
       </c>
       <c r="M125" s="1"/>
@@ -14594,20 +14943,20 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
       <c r="S125" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>7.4</v>
       </c>
       <c r="T125" s="5"/>
       <c r="U125" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V125" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>62.486486486486491</v>
       </c>
       <c r="W125" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>62.486486486486491</v>
       </c>
       <c r="X125" s="1">
@@ -14642,10 +14991,13 @@
       </c>
       <c r="AH125" s="1"/>
       <c r="AI125" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ125" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ125" s="1">
+        <f t="shared" si="28"/>
+        <v>170.16363636363636</v>
+      </c>
       <c r="AK125" s="1"/>
       <c r="AL125" s="1"/>
       <c r="AM125" s="1"/>
@@ -14690,7 +15042,7 @@
         <v>14.4</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.8119999999999994</v>
       </c>
       <c r="M126" s="1"/>
@@ -14704,23 +15056,23 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
       <c r="S126" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3.8424</v>
       </c>
       <c r="T126" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>14.6953</v>
       </c>
       <c r="U126" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>14.6953</v>
       </c>
       <c r="V126" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W126" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>8.175489277534874</v>
       </c>
       <c r="X126" s="1">
@@ -14755,10 +15107,13 @@
       </c>
       <c r="AH126" s="1"/>
       <c r="AI126" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>15</v>
       </c>
-      <c r="AJ126" s="1"/>
+      <c r="AJ126" s="1">
+        <f t="shared" si="28"/>
+        <v>17.922545454545457</v>
+      </c>
       <c r="AK126" s="1"/>
       <c r="AL126" s="1"/>
       <c r="AM126" s="1"/>
@@ -14803,7 +15158,7 @@
         <v>133</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-19</v>
       </c>
       <c r="M127" s="1"/>
@@ -14817,23 +15172,23 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
       <c r="S127" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>22.8</v>
       </c>
       <c r="T127" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>66.600000000000023</v>
       </c>
       <c r="U127" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>66.600000000000023</v>
       </c>
       <c r="V127" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W127" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>9.0789473684210531</v>
       </c>
       <c r="X127" s="1">
@@ -14868,10 +15223,13 @@
       </c>
       <c r="AH127" s="1"/>
       <c r="AI127" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
-      <c r="AJ127" s="1"/>
+      <c r="AJ127" s="1">
+        <f t="shared" si="28"/>
+        <v>106.65454545454546</v>
+      </c>
       <c r="AK127" s="1"/>
       <c r="AL127" s="1"/>
       <c r="AM127" s="1"/>
@@ -14914,7 +15272,7 @@
         <v>61</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-15</v>
       </c>
       <c r="M128" s="1"/>
@@ -14928,22 +15286,22 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
       <c r="S128" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="T128" s="5">
         <v>10</v>
       </c>
       <c r="U128" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
       <c r="V128" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12.717391304347828</v>
       </c>
       <c r="W128" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>11.630434782608697</v>
       </c>
       <c r="X128" s="1">
@@ -14978,10 +15336,13 @@
       </c>
       <c r="AH128" s="1"/>
       <c r="AI128" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="AJ128" s="1"/>
+      <c r="AJ128" s="1">
+        <f t="shared" si="28"/>
+        <v>55.872727272727268</v>
+      </c>
       <c r="AK128" s="1"/>
       <c r="AL128" s="1"/>
       <c r="AM128" s="1"/>
@@ -14994,7 +15355,7 @@
       <c r="AT128" s="1"/>
     </row>
     <row r="129" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="1" t="s">
         <v>172</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -15014,7 +15375,7 @@
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
       <c r="L129" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M129" s="1"/>
@@ -15026,20 +15387,20 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T129" s="5"/>
       <c r="U129" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V129" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W129" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X129" s="1">
@@ -15076,10 +15437,13 @@
         <v>158</v>
       </c>
       <c r="AI129" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ129" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ129" s="1">
+        <f t="shared" si="28"/>
+        <v>3.1818181818181822E-2</v>
+      </c>
       <c r="AK129" s="1"/>
       <c r="AL129" s="1"/>
       <c r="AM129" s="1"/>
@@ -15092,7 +15456,7 @@
       <c r="AT129" s="1"/>
     </row>
     <row r="130" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A130" s="13" t="s">
+      <c r="A130" s="1" t="s">
         <v>173</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -15112,7 +15476,7 @@
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
       <c r="L130" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M130" s="1"/>
@@ -15124,20 +15488,20 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
       <c r="S130" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T130" s="5"/>
       <c r="U130" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V130" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W130" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X130" s="1">
@@ -15174,10 +15538,13 @@
         <v>158</v>
       </c>
       <c r="AI130" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ130" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ130" s="1">
+        <f t="shared" si="28"/>
+        <v>4.1363636363636366E-2</v>
+      </c>
       <c r="AK130" s="1"/>
       <c r="AL130" s="1"/>
       <c r="AM130" s="1"/>
@@ -15190,7 +15557,7 @@
       <c r="AT130" s="1"/>
     </row>
     <row r="131" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -15210,7 +15577,7 @@
       <c r="J131" s="1"/>
       <c r="K131" s="1"/>
       <c r="L131" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M131" s="1"/>
@@ -15222,20 +15589,20 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T131" s="5"/>
       <c r="U131" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V131" s="1" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W131" s="1" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X131" s="1">
@@ -15272,10 +15639,13 @@
         <v>158</v>
       </c>
       <c r="AI131" s="1">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AJ131" s="1"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AJ131" s="1">
+        <f t="shared" si="28"/>
+        <v>3.1818181818181822E-2</v>
+      </c>
       <c r="AK131" s="1"/>
       <c r="AL131" s="1"/>
       <c r="AM131" s="1"/>
